--- a/ICET_Ubicacion_Docentes_Bachillerato.xlsx
+++ b/ICET_Ubicacion_Docentes_Bachillerato.xlsx
@@ -3427,7 +3427,7 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="36" customWidth="1" min="10" max="10"/>
     <col width="36" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="27" customWidth="1" min="12" max="12"/>
     <col width="36" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="24" customWidth="1" min="15" max="15"/>
@@ -3562,7 +3562,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -3627,7 +3627,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -3692,7 +3692,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -3757,7 +3757,7 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -3822,7 +3822,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -3887,7 +3887,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3952,7 +3952,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -4017,7 +4017,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4082,7 +4082,7 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -4147,7 +4147,7 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4212,7 +4212,7 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -4273,7 +4273,7 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -4334,7 +4334,7 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -4395,7 +4395,7 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-01</t>
+          <t>ÉNFASIS 7°-1</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-01</t>
+          <t>ÉNFASIS 7°-1</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-02</t>
+          <t>ÉNFASIS 7°-2</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-02</t>
+          <t>ÉNFASIS 7°-2</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-03</t>
+          <t>ÉNFASIS 7°-3</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-03</t>
+          <t>ÉNFASIS 7°-3</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -5186,7 +5186,7 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
@@ -5251,7 +5251,7 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -5316,7 +5316,7 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
@@ -5381,7 +5381,7 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -5446,7 +5446,7 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
@@ -5511,7 +5511,7 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -5576,7 +5576,7 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
@@ -5641,7 +5641,7 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -5706,7 +5706,7 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
@@ -5771,7 +5771,7 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -5836,7 +5836,7 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
@@ -5897,7 +5897,7 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
@@ -5958,7 +5958,7 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
@@ -6019,7 +6019,7 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -6088,7 +6088,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-01</t>
+          <t>ÉNFASIS 7°-1</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-01</t>
+          <t>ÉNFASIS 7°-1</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-02</t>
+          <t>ÉNFASIS 7°-2</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-02</t>
+          <t>ÉNFASIS 7°-2</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-03</t>
+          <t>ÉNFASIS 7°-3</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-03</t>
+          <t>ÉNFASIS 7°-3</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -6810,7 +6810,7 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
@@ -6871,7 +6871,7 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
@@ -6932,7 +6932,7 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
@@ -6993,7 +6993,7 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
@@ -7054,7 +7054,7 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M54" t="inlineStr"/>
@@ -7119,7 +7119,7 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -7184,7 +7184,7 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
@@ -7245,7 +7245,7 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
@@ -7306,7 +7306,7 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
@@ -7371,7 +7371,7 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -7436,7 +7436,7 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
@@ -7497,7 +7497,7 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M61" t="inlineStr"/>
@@ -7562,7 +7562,7 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7627,7 +7627,7 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
@@ -7688,7 +7688,7 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
@@ -7749,7 +7749,7 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M65" t="inlineStr"/>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -8394,7 +8394,7 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
@@ -8455,7 +8455,7 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
@@ -8516,7 +8516,7 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
@@ -8577,7 +8577,7 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
@@ -8638,7 +8638,7 @@
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
@@ -8703,7 +8703,7 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -8768,7 +8768,7 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
@@ -8829,7 +8829,7 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
@@ -8890,7 +8890,7 @@
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
@@ -8955,7 +8955,7 @@
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -9020,7 +9020,7 @@
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
@@ -9081,7 +9081,7 @@
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
@@ -9146,7 +9146,7 @@
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -9211,7 +9211,7 @@
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
@@ -9272,7 +9272,7 @@
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
@@ -9333,7 +9333,7 @@
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
@@ -9402,7 +9402,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -9621,7 +9621,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -9767,7 +9767,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -9840,7 +9840,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -9978,7 +9978,7 @@
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
@@ -10043,7 +10043,7 @@
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -10108,7 +10108,7 @@
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
@@ -10169,7 +10169,7 @@
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
@@ -10230,7 +10230,7 @@
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
@@ -10291,7 +10291,7 @@
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
@@ -10356,7 +10356,7 @@
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -10425,7 +10425,7 @@
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -10490,7 +10490,7 @@
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
@@ -10551,7 +10551,7 @@
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
@@ -10612,7 +10612,7 @@
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
@@ -10673,7 +10673,7 @@
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
@@ -10734,7 +10734,7 @@
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
@@ -10795,7 +10795,7 @@
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
@@ -10864,7 +10864,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-04</t>
+          <t>ÉNFASIS 7°-4</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -10937,7 +10937,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-04</t>
+          <t>ÉNFASIS 7°-4</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -11083,7 +11083,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -11375,7 +11375,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -11878,7 +11878,7 @@
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M126" t="inlineStr"/>
@@ -11943,7 +11943,7 @@
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -12008,7 +12008,7 @@
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M128" t="inlineStr"/>
@@ -12069,7 +12069,7 @@
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M129" t="inlineStr"/>
@@ -12130,7 +12130,7 @@
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M130" t="inlineStr"/>
@@ -12191,7 +12191,7 @@
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M131" t="inlineStr"/>
@@ -12256,7 +12256,7 @@
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -12325,7 +12325,7 @@
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -12390,7 +12390,7 @@
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M134" t="inlineStr"/>
@@ -12451,7 +12451,7 @@
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M135" t="inlineStr"/>
@@ -12512,7 +12512,7 @@
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M136" t="inlineStr"/>
@@ -12573,7 +12573,7 @@
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M137" t="inlineStr"/>
@@ -12634,7 +12634,7 @@
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M138" t="inlineStr"/>
@@ -12695,7 +12695,7 @@
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M139" t="inlineStr"/>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-04</t>
+          <t>ÉNFASIS 7°-4</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -12837,7 +12837,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-04</t>
+          <t>ÉNFASIS 7°-4</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -12983,7 +12983,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -13056,7 +13056,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -13129,7 +13129,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -13202,7 +13202,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -13348,7 +13348,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -13421,7 +13421,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -13494,7 +13494,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -13567,7 +13567,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -13782,7 +13782,7 @@
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -13847,7 +13847,7 @@
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M155" t="inlineStr"/>
@@ -13908,7 +13908,7 @@
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M156" t="inlineStr"/>
@@ -13969,7 +13969,7 @@
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M157" t="inlineStr"/>
@@ -14034,7 +14034,7 @@
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -14099,7 +14099,7 @@
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M159" t="inlineStr"/>
@@ -14160,7 +14160,7 @@
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M160" t="inlineStr"/>
@@ -14221,7 +14221,7 @@
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M161" t="inlineStr"/>
@@ -14286,7 +14286,7 @@
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -14351,7 +14351,7 @@
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M163" t="inlineStr"/>
@@ -14412,7 +14412,7 @@
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M164" t="inlineStr"/>
@@ -14473,7 +14473,7 @@
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M165" t="inlineStr"/>
@@ -14538,7 +14538,7 @@
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -14603,7 +14603,7 @@
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M167" t="inlineStr"/>
@@ -14664,7 +14664,7 @@
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M168" t="inlineStr"/>
@@ -14725,7 +14725,7 @@
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M169" t="inlineStr"/>
@@ -14794,7 +14794,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -14867,7 +14867,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -14940,7 +14940,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -15013,7 +15013,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -15086,7 +15086,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -15305,7 +15305,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -15374,7 +15374,7 @@
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -15439,7 +15439,7 @@
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M179" t="inlineStr"/>
@@ -15500,7 +15500,7 @@
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M180" t="inlineStr"/>
@@ -15561,7 +15561,7 @@
       <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M181" t="inlineStr"/>
@@ -15626,7 +15626,7 @@
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -15691,7 +15691,7 @@
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M183" t="inlineStr"/>
@@ -15752,7 +15752,7 @@
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M184" t="inlineStr"/>
@@ -15813,7 +15813,7 @@
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M185" t="inlineStr"/>
@@ -15878,7 +15878,7 @@
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -15943,7 +15943,7 @@
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M187" t="inlineStr"/>
@@ -16004,7 +16004,7 @@
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M188" t="inlineStr"/>
@@ -16065,7 +16065,7 @@
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M189" t="inlineStr"/>
@@ -16130,7 +16130,7 @@
       <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -16195,7 +16195,7 @@
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M191" t="inlineStr"/>
@@ -16256,7 +16256,7 @@
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M192" t="inlineStr"/>
@@ -16317,7 +16317,7 @@
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M193" t="inlineStr"/>
@@ -16386,7 +16386,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -16459,7 +16459,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -16532,7 +16532,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -16605,7 +16605,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -16678,7 +16678,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -16751,7 +16751,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -16824,7 +16824,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -16962,7 +16962,7 @@
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M202" t="inlineStr"/>
@@ -17023,7 +17023,7 @@
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M203" t="inlineStr"/>
@@ -17084,7 +17084,7 @@
       <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M204" t="inlineStr"/>
@@ -17145,7 +17145,7 @@
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M205" t="inlineStr"/>
@@ -17206,7 +17206,7 @@
       <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M206" t="inlineStr"/>
@@ -17267,7 +17267,7 @@
       <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M207" t="inlineStr"/>
@@ -17328,7 +17328,7 @@
       <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M208" t="inlineStr"/>
@@ -17389,7 +17389,7 @@
       <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M209" t="inlineStr"/>
@@ -17450,7 +17450,7 @@
       <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M210" t="inlineStr"/>
@@ -17515,7 +17515,7 @@
       <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -17580,7 +17580,7 @@
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M212" t="inlineStr"/>
@@ -17649,7 +17649,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-01</t>
+          <t>ÉNFASIS 7°-1</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -17722,7 +17722,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-01</t>
+          <t>ÉNFASIS 7°-1</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
@@ -17795,7 +17795,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-02</t>
+          <t>ÉNFASIS 7°-2</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -17868,7 +17868,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-02</t>
+          <t>ÉNFASIS 7°-2</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
@@ -17941,7 +17941,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-03</t>
+          <t>ÉNFASIS 7°-3</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -18014,7 +18014,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-03</t>
+          <t>ÉNFASIS 7°-3</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -18087,7 +18087,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -18160,7 +18160,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -18233,7 +18233,7 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -18379,7 +18379,7 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
@@ -18452,7 +18452,7 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
@@ -18525,7 +18525,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
@@ -18598,7 +18598,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -18671,7 +18671,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -18744,7 +18744,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -18817,7 +18817,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -18890,7 +18890,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -18955,7 +18955,7 @@
       <c r="K231" t="inlineStr"/>
       <c r="L231" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M231" t="inlineStr"/>
@@ -19016,7 +19016,7 @@
       <c r="K232" t="inlineStr"/>
       <c r="L232" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M232" t="inlineStr"/>
@@ -19077,7 +19077,7 @@
       <c r="K233" t="inlineStr"/>
       <c r="L233" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M233" t="inlineStr"/>
@@ -19138,7 +19138,7 @@
       <c r="K234" t="inlineStr"/>
       <c r="L234" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M234" t="inlineStr"/>
@@ -19199,7 +19199,7 @@
       <c r="K235" t="inlineStr"/>
       <c r="L235" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M235" t="inlineStr"/>
@@ -19260,7 +19260,7 @@
       <c r="K236" t="inlineStr"/>
       <c r="L236" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M236" t="inlineStr"/>
@@ -19321,7 +19321,7 @@
       <c r="K237" t="inlineStr"/>
       <c r="L237" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M237" t="inlineStr"/>
@@ -19382,7 +19382,7 @@
       <c r="K238" t="inlineStr"/>
       <c r="L238" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M238" t="inlineStr"/>
@@ -19443,7 +19443,7 @@
       <c r="K239" t="inlineStr"/>
       <c r="L239" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M239" t="inlineStr"/>
@@ -19508,7 +19508,7 @@
       <c r="K240" t="inlineStr"/>
       <c r="L240" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -19573,7 +19573,7 @@
       <c r="K241" t="inlineStr"/>
       <c r="L241" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M241" t="inlineStr"/>
@@ -19642,7 +19642,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-01</t>
+          <t>ÉNFASIS 7°-1</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -19715,7 +19715,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-01</t>
+          <t>ÉNFASIS 7°-1</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -19788,7 +19788,7 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-02</t>
+          <t>ÉNFASIS 7°-2</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
@@ -19861,7 +19861,7 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-02</t>
+          <t>ÉNFASIS 7°-2</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
@@ -19934,7 +19934,7 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-03</t>
+          <t>ÉNFASIS 7°-3</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
@@ -20007,7 +20007,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-03</t>
+          <t>ÉNFASIS 7°-3</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
@@ -20080,7 +20080,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -20153,7 +20153,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -20226,7 +20226,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -20299,7 +20299,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -20372,7 +20372,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -20445,7 +20445,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -20518,7 +20518,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -20591,7 +20591,7 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -20737,7 +20737,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -20810,7 +20810,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -20883,7 +20883,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
@@ -20948,7 +20948,7 @@
       <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M260" t="inlineStr"/>
@@ -21009,7 +21009,7 @@
       <c r="K261" t="inlineStr"/>
       <c r="L261" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M261" t="inlineStr"/>
@@ -21070,7 +21070,7 @@
       <c r="K262" t="inlineStr"/>
       <c r="L262" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M262" t="inlineStr"/>
@@ -21131,7 +21131,7 @@
       <c r="K263" t="inlineStr"/>
       <c r="L263" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M263" t="inlineStr"/>
@@ -21192,7 +21192,7 @@
       <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M264" t="inlineStr"/>
@@ -21257,7 +21257,7 @@
       <c r="K265" t="inlineStr"/>
       <c r="L265" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
@@ -21326,7 +21326,7 @@
       <c r="K266" t="inlineStr"/>
       <c r="L266" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
@@ -21395,7 +21395,7 @@
       <c r="K267" t="inlineStr"/>
       <c r="L267" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
@@ -21460,7 +21460,7 @@
       <c r="K268" t="inlineStr"/>
       <c r="L268" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M268" t="inlineStr"/>
@@ -21521,7 +21521,7 @@
       <c r="K269" t="inlineStr"/>
       <c r="L269" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M269" t="inlineStr"/>
@@ -21582,7 +21582,7 @@
       <c r="K270" t="inlineStr"/>
       <c r="L270" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M270" t="inlineStr"/>
@@ -21647,7 +21647,7 @@
       <c r="K271" t="inlineStr"/>
       <c r="L271" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -21712,7 +21712,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M272" t="inlineStr"/>
@@ -21777,7 +21777,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -21846,7 +21846,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -21919,7 +21919,7 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
@@ -22065,7 +22065,7 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
@@ -22138,7 +22138,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
@@ -22211,7 +22211,7 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
@@ -22284,7 +22284,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
@@ -22357,7 +22357,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
@@ -22430,7 +22430,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -22503,7 +22503,7 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
@@ -22576,7 +22576,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -22649,7 +22649,7 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -22722,7 +22722,7 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -22787,7 +22787,7 @@
       <c r="K287" t="inlineStr"/>
       <c r="L287" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M287" t="inlineStr"/>
@@ -22848,7 +22848,7 @@
       <c r="K288" t="inlineStr"/>
       <c r="L288" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M288" t="inlineStr"/>
@@ -22909,7 +22909,7 @@
       <c r="K289" t="inlineStr"/>
       <c r="L289" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M289" t="inlineStr"/>
@@ -22970,7 +22970,7 @@
       <c r="K290" t="inlineStr"/>
       <c r="L290" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M290" t="inlineStr"/>
@@ -23031,7 +23031,7 @@
       <c r="K291" t="inlineStr"/>
       <c r="L291" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M291" t="inlineStr"/>
@@ -23096,7 +23096,7 @@
       <c r="K292" t="inlineStr"/>
       <c r="L292" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
@@ -23165,7 +23165,7 @@
       <c r="K293" t="inlineStr"/>
       <c r="L293" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
@@ -23234,7 +23234,7 @@
       <c r="K294" t="inlineStr"/>
       <c r="L294" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
@@ -23299,7 +23299,7 @@
       <c r="K295" t="inlineStr"/>
       <c r="L295" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M295" t="inlineStr"/>
@@ -23360,7 +23360,7 @@
       <c r="K296" t="inlineStr"/>
       <c r="L296" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M296" t="inlineStr"/>
@@ -23421,7 +23421,7 @@
       <c r="K297" t="inlineStr"/>
       <c r="L297" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M297" t="inlineStr"/>
@@ -23486,7 +23486,7 @@
       <c r="K298" t="inlineStr"/>
       <c r="L298" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
@@ -23551,7 +23551,7 @@
       <c r="K299" t="inlineStr"/>
       <c r="L299" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M299" t="inlineStr"/>
@@ -23616,7 +23616,7 @@
       <c r="K300" t="inlineStr"/>
       <c r="L300" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
@@ -23685,7 +23685,7 @@
       <c r="K301" t="inlineStr"/>
       <c r="L301" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
@@ -23758,7 +23758,7 @@
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
@@ -23831,7 +23831,7 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
@@ -23904,7 +23904,7 @@
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
@@ -23977,7 +23977,7 @@
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
@@ -24050,7 +24050,7 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
@@ -24123,7 +24123,7 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
@@ -24269,7 +24269,7 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
@@ -24342,7 +24342,7 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
@@ -24415,7 +24415,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -24488,7 +24488,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -24561,7 +24561,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -24626,7 +24626,7 @@
       <c r="K314" t="inlineStr"/>
       <c r="L314" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M314" t="inlineStr"/>
@@ -24687,7 +24687,7 @@
       <c r="K315" t="inlineStr"/>
       <c r="L315" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M315" t="inlineStr"/>
@@ -24748,7 +24748,7 @@
       <c r="K316" t="inlineStr"/>
       <c r="L316" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M316" t="inlineStr"/>
@@ -24809,7 +24809,7 @@
       <c r="K317" t="inlineStr"/>
       <c r="L317" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M317" t="inlineStr"/>
@@ -24874,7 +24874,7 @@
       <c r="K318" t="inlineStr"/>
       <c r="L318" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
@@ -24943,7 +24943,7 @@
       <c r="K319" t="inlineStr"/>
       <c r="L319" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
@@ -25008,7 +25008,7 @@
       <c r="K320" t="inlineStr"/>
       <c r="L320" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M320" t="inlineStr"/>
@@ -25069,7 +25069,7 @@
       <c r="K321" t="inlineStr"/>
       <c r="L321" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M321" t="inlineStr"/>
@@ -25130,7 +25130,7 @@
       <c r="K322" t="inlineStr"/>
       <c r="L322" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M322" t="inlineStr"/>
@@ -25191,7 +25191,7 @@
       <c r="K323" t="inlineStr"/>
       <c r="L323" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M323" t="inlineStr"/>
@@ -25252,7 +25252,7 @@
       <c r="K324" t="inlineStr"/>
       <c r="L324" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M324" t="inlineStr"/>
@@ -25313,7 +25313,7 @@
       <c r="K325" t="inlineStr"/>
       <c r="L325" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M325" t="inlineStr"/>
@@ -25378,7 +25378,7 @@
       <c r="K326" t="inlineStr"/>
       <c r="L326" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
@@ -25443,7 +25443,7 @@
       <c r="K327" t="inlineStr"/>
       <c r="L327" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M327" t="inlineStr"/>
@@ -25504,7 +25504,7 @@
       <c r="K328" t="inlineStr"/>
       <c r="L328" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M328" t="inlineStr"/>
@@ -25573,7 +25573,7 @@
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-04</t>
+          <t>ÉNFASIS 7°-4</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
@@ -25646,7 +25646,7 @@
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-04</t>
+          <t>ÉNFASIS 7°-4</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
@@ -25719,7 +25719,7 @@
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
@@ -25792,7 +25792,7 @@
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
@@ -25865,7 +25865,7 @@
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
@@ -25938,7 +25938,7 @@
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
@@ -26011,7 +26011,7 @@
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
@@ -26084,7 +26084,7 @@
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
@@ -26157,7 +26157,7 @@
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
@@ -26230,7 +26230,7 @@
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
@@ -26295,7 +26295,7 @@
       <c r="K339" t="inlineStr"/>
       <c r="L339" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M339" t="inlineStr"/>
@@ -26356,7 +26356,7 @@
       <c r="K340" t="inlineStr"/>
       <c r="L340" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M340" t="inlineStr"/>
@@ -26417,7 +26417,7 @@
       <c r="K341" t="inlineStr"/>
       <c r="L341" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M341" t="inlineStr"/>
@@ -26478,7 +26478,7 @@
       <c r="K342" t="inlineStr"/>
       <c r="L342" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M342" t="inlineStr"/>
@@ -26543,7 +26543,7 @@
       <c r="K343" t="inlineStr"/>
       <c r="L343" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
@@ -26612,7 +26612,7 @@
       <c r="K344" t="inlineStr"/>
       <c r="L344" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
@@ -26677,7 +26677,7 @@
       <c r="K345" t="inlineStr"/>
       <c r="L345" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M345" t="inlineStr"/>
@@ -26738,7 +26738,7 @@
       <c r="K346" t="inlineStr"/>
       <c r="L346" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M346" t="inlineStr"/>
@@ -26799,7 +26799,7 @@
       <c r="K347" t="inlineStr"/>
       <c r="L347" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M347" t="inlineStr"/>
@@ -26860,7 +26860,7 @@
       <c r="K348" t="inlineStr"/>
       <c r="L348" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M348" t="inlineStr"/>
@@ -26921,7 +26921,7 @@
       <c r="K349" t="inlineStr"/>
       <c r="L349" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M349" t="inlineStr"/>
@@ -26982,7 +26982,7 @@
       <c r="K350" t="inlineStr"/>
       <c r="L350" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M350" t="inlineStr"/>
@@ -27047,7 +27047,7 @@
       <c r="K351" t="inlineStr"/>
       <c r="L351" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
@@ -27112,7 +27112,7 @@
       <c r="K352" t="inlineStr"/>
       <c r="L352" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M352" t="inlineStr"/>
@@ -27173,7 +27173,7 @@
       <c r="K353" t="inlineStr"/>
       <c r="L353" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M353" t="inlineStr"/>
@@ -27242,7 +27242,7 @@
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-04</t>
+          <t>ÉNFASIS 7°-4</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
@@ -27315,7 +27315,7 @@
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-04</t>
+          <t>ÉNFASIS 7°-4</t>
         </is>
       </c>
       <c r="M355" t="inlineStr">
@@ -27388,7 +27388,7 @@
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M356" t="inlineStr">
@@ -27461,7 +27461,7 @@
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M357" t="inlineStr">
@@ -27534,7 +27534,7 @@
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
@@ -27607,7 +27607,7 @@
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">
@@ -27680,7 +27680,7 @@
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M360" t="inlineStr">
@@ -27753,7 +27753,7 @@
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
@@ -27826,7 +27826,7 @@
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
@@ -27899,7 +27899,7 @@
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
@@ -27968,7 +27968,7 @@
       <c r="K364" t="inlineStr"/>
       <c r="L364" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
@@ -28033,7 +28033,7 @@
       <c r="K365" t="inlineStr"/>
       <c r="L365" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M365" t="inlineStr"/>
@@ -28098,7 +28098,7 @@
       <c r="K366" t="inlineStr"/>
       <c r="L366" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M366" t="inlineStr">
@@ -28163,7 +28163,7 @@
       <c r="K367" t="inlineStr"/>
       <c r="L367" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M367" t="inlineStr"/>
@@ -28224,7 +28224,7 @@
       <c r="K368" t="inlineStr"/>
       <c r="L368" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M368" t="inlineStr"/>
@@ -28285,7 +28285,7 @@
       <c r="K369" t="inlineStr"/>
       <c r="L369" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M369" t="inlineStr"/>
@@ -28350,7 +28350,7 @@
       <c r="K370" t="inlineStr"/>
       <c r="L370" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M370" t="inlineStr">
@@ -28419,7 +28419,7 @@
       <c r="K371" t="inlineStr"/>
       <c r="L371" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
@@ -28484,7 +28484,7 @@
       <c r="K372" t="inlineStr"/>
       <c r="L372" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M372" t="inlineStr"/>
@@ -28545,7 +28545,7 @@
       <c r="K373" t="inlineStr"/>
       <c r="L373" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M373" t="inlineStr"/>
@@ -28606,7 +28606,7 @@
       <c r="K374" t="inlineStr"/>
       <c r="L374" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M374" t="inlineStr"/>
@@ -28667,7 +28667,7 @@
       <c r="K375" t="inlineStr"/>
       <c r="L375" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M375" t="inlineStr"/>
@@ -28728,7 +28728,7 @@
       <c r="K376" t="inlineStr"/>
       <c r="L376" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M376" t="inlineStr"/>
@@ -28793,7 +28793,7 @@
       <c r="K377" t="inlineStr"/>
       <c r="L377" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
@@ -28866,7 +28866,7 @@
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-01</t>
+          <t>ÉNFASIS 6°-1</t>
         </is>
       </c>
       <c r="M378" t="inlineStr">
@@ -28939,7 +28939,7 @@
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-01</t>
+          <t>ÉNFASIS 6°-1</t>
         </is>
       </c>
       <c r="M379" t="inlineStr">
@@ -29012,7 +29012,7 @@
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-02</t>
+          <t>ÉNFASIS 6°-2</t>
         </is>
       </c>
       <c r="M380" t="inlineStr">
@@ -29085,7 +29085,7 @@
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-02</t>
+          <t>ÉNFASIS 6°-2</t>
         </is>
       </c>
       <c r="M381" t="inlineStr">
@@ -29158,7 +29158,7 @@
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M382" t="inlineStr">
@@ -29231,7 +29231,7 @@
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M383" t="inlineStr">
@@ -29304,7 +29304,7 @@
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M384" t="inlineStr">
@@ -29377,7 +29377,7 @@
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M385" t="inlineStr">
@@ -29450,7 +29450,7 @@
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M386" t="inlineStr">
@@ -29523,7 +29523,7 @@
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M387" t="inlineStr">
@@ -29596,7 +29596,7 @@
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M388" t="inlineStr">
@@ -29669,7 +29669,7 @@
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M389" t="inlineStr">
@@ -29738,7 +29738,7 @@
       <c r="K390" t="inlineStr"/>
       <c r="L390" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M390" t="inlineStr">
@@ -29803,7 +29803,7 @@
       <c r="K391" t="inlineStr"/>
       <c r="L391" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M391" t="inlineStr"/>
@@ -29868,7 +29868,7 @@
       <c r="K392" t="inlineStr"/>
       <c r="L392" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M392" t="inlineStr">
@@ -29933,7 +29933,7 @@
       <c r="K393" t="inlineStr"/>
       <c r="L393" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M393" t="inlineStr"/>
@@ -29994,7 +29994,7 @@
       <c r="K394" t="inlineStr"/>
       <c r="L394" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M394" t="inlineStr"/>
@@ -30055,7 +30055,7 @@
       <c r="K395" t="inlineStr"/>
       <c r="L395" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M395" t="inlineStr"/>
@@ -30120,7 +30120,7 @@
       <c r="K396" t="inlineStr"/>
       <c r="L396" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M396" t="inlineStr">
@@ -30189,7 +30189,7 @@
       <c r="K397" t="inlineStr"/>
       <c r="L397" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M397" t="inlineStr">
@@ -30254,7 +30254,7 @@
       <c r="K398" t="inlineStr"/>
       <c r="L398" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M398" t="inlineStr"/>
@@ -30315,7 +30315,7 @@
       <c r="K399" t="inlineStr"/>
       <c r="L399" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M399" t="inlineStr"/>
@@ -30376,7 +30376,7 @@
       <c r="K400" t="inlineStr"/>
       <c r="L400" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M400" t="inlineStr"/>
@@ -30437,7 +30437,7 @@
       <c r="K401" t="inlineStr"/>
       <c r="L401" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M401" t="inlineStr"/>
@@ -30498,7 +30498,7 @@
       <c r="K402" t="inlineStr"/>
       <c r="L402" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M402" t="inlineStr"/>
@@ -30563,7 +30563,7 @@
       <c r="K403" t="inlineStr"/>
       <c r="L403" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M403" t="inlineStr">
@@ -30636,7 +30636,7 @@
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-01</t>
+          <t>ÉNFASIS 6°-1</t>
         </is>
       </c>
       <c r="M404" t="inlineStr">
@@ -30709,7 +30709,7 @@
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-01</t>
+          <t>ÉNFASIS 6°-1</t>
         </is>
       </c>
       <c r="M405" t="inlineStr">
@@ -30782,7 +30782,7 @@
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-02</t>
+          <t>ÉNFASIS 6°-2</t>
         </is>
       </c>
       <c r="M406" t="inlineStr">
@@ -30855,7 +30855,7 @@
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-02</t>
+          <t>ÉNFASIS 6°-2</t>
         </is>
       </c>
       <c r="M407" t="inlineStr">
@@ -30928,7 +30928,7 @@
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M408" t="inlineStr">
@@ -31001,7 +31001,7 @@
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M409" t="inlineStr">
@@ -31074,7 +31074,7 @@
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M410" t="inlineStr">
@@ -31147,7 +31147,7 @@
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M411" t="inlineStr">
@@ -31220,7 +31220,7 @@
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M412" t="inlineStr">
@@ -31293,7 +31293,7 @@
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M413" t="inlineStr">
@@ -31366,7 +31366,7 @@
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M414" t="inlineStr">
@@ -31439,7 +31439,7 @@
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M415" t="inlineStr">
@@ -31504,7 +31504,7 @@
       <c r="K416" t="inlineStr"/>
       <c r="L416" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M416" t="inlineStr"/>
@@ -31565,7 +31565,7 @@
       <c r="K417" t="inlineStr"/>
       <c r="L417" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M417" t="inlineStr"/>
@@ -31626,7 +31626,7 @@
       <c r="K418" t="inlineStr"/>
       <c r="L418" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M418" t="inlineStr"/>
@@ -31687,7 +31687,7 @@
       <c r="K419" t="inlineStr"/>
       <c r="L419" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M419" t="inlineStr"/>
@@ -31748,7 +31748,7 @@
       <c r="K420" t="inlineStr"/>
       <c r="L420" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M420" t="inlineStr"/>
@@ -31809,7 +31809,7 @@
       <c r="K421" t="inlineStr"/>
       <c r="L421" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M421" t="inlineStr"/>
@@ -31870,7 +31870,7 @@
       <c r="K422" t="inlineStr"/>
       <c r="L422" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M422" t="inlineStr"/>
@@ -31931,7 +31931,7 @@
       <c r="K423" t="inlineStr"/>
       <c r="L423" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M423" t="inlineStr"/>
@@ -31992,7 +31992,7 @@
       <c r="K424" t="inlineStr"/>
       <c r="L424" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M424" t="inlineStr"/>
@@ -32057,7 +32057,7 @@
       <c r="K425" t="inlineStr"/>
       <c r="L425" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M425" t="inlineStr">
@@ -32122,7 +32122,7 @@
       <c r="K426" t="inlineStr"/>
       <c r="L426" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M426" t="inlineStr"/>
@@ -32183,7 +32183,7 @@
       <c r="K427" t="inlineStr"/>
       <c r="L427" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M427" t="inlineStr"/>
@@ -32248,7 +32248,7 @@
       <c r="K428" t="inlineStr"/>
       <c r="L428" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M428" t="inlineStr">
@@ -32321,7 +32321,7 @@
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-01</t>
+          <t>ÉNFASIS 7°-1</t>
         </is>
       </c>
       <c r="M429" t="inlineStr">
@@ -32394,7 +32394,7 @@
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-01</t>
+          <t>ÉNFASIS 7°-1</t>
         </is>
       </c>
       <c r="M430" t="inlineStr">
@@ -32467,7 +32467,7 @@
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-02</t>
+          <t>ÉNFASIS 7°-2</t>
         </is>
       </c>
       <c r="M431" t="inlineStr">
@@ -32540,7 +32540,7 @@
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-02</t>
+          <t>ÉNFASIS 7°-2</t>
         </is>
       </c>
       <c r="M432" t="inlineStr">
@@ -32613,7 +32613,7 @@
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-03</t>
+          <t>ÉNFASIS 7°-3</t>
         </is>
       </c>
       <c r="M433" t="inlineStr">
@@ -32686,7 +32686,7 @@
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-03</t>
+          <t>ÉNFASIS 7°-3</t>
         </is>
       </c>
       <c r="M434" t="inlineStr">
@@ -32759,7 +32759,7 @@
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M435" t="inlineStr">
@@ -32832,7 +32832,7 @@
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M436" t="inlineStr">
@@ -32905,7 +32905,7 @@
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M437" t="inlineStr">
@@ -32978,7 +32978,7 @@
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M438" t="inlineStr">
@@ -33043,7 +33043,7 @@
       <c r="K439" t="inlineStr"/>
       <c r="L439" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M439" t="inlineStr"/>
@@ -33104,7 +33104,7 @@
       <c r="K440" t="inlineStr"/>
       <c r="L440" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M440" t="inlineStr"/>
@@ -33165,7 +33165,7 @@
       <c r="K441" t="inlineStr"/>
       <c r="L441" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M441" t="inlineStr"/>
@@ -33226,7 +33226,7 @@
       <c r="K442" t="inlineStr"/>
       <c r="L442" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M442" t="inlineStr"/>
@@ -33287,7 +33287,7 @@
       <c r="K443" t="inlineStr"/>
       <c r="L443" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M443" t="inlineStr"/>
@@ -33348,7 +33348,7 @@
       <c r="K444" t="inlineStr"/>
       <c r="L444" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M444" t="inlineStr"/>
@@ -33409,7 +33409,7 @@
       <c r="K445" t="inlineStr"/>
       <c r="L445" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M445" t="inlineStr"/>
@@ -33470,7 +33470,7 @@
       <c r="K446" t="inlineStr"/>
       <c r="L446" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M446" t="inlineStr"/>
@@ -33531,7 +33531,7 @@
       <c r="K447" t="inlineStr"/>
       <c r="L447" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M447" t="inlineStr"/>
@@ -33596,7 +33596,7 @@
       <c r="K448" t="inlineStr"/>
       <c r="L448" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M448" t="inlineStr">
@@ -33661,7 +33661,7 @@
       <c r="K449" t="inlineStr"/>
       <c r="L449" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M449" t="inlineStr"/>
@@ -33722,7 +33722,7 @@
       <c r="K450" t="inlineStr"/>
       <c r="L450" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M450" t="inlineStr"/>
@@ -33787,7 +33787,7 @@
       <c r="K451" t="inlineStr"/>
       <c r="L451" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M451" t="inlineStr">
@@ -33860,7 +33860,7 @@
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-01</t>
+          <t>ÉNFASIS 7°-1</t>
         </is>
       </c>
       <c r="M452" t="inlineStr">
@@ -33933,7 +33933,7 @@
       </c>
       <c r="L453" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-01</t>
+          <t>ÉNFASIS 7°-1</t>
         </is>
       </c>
       <c r="M453" t="inlineStr">
@@ -34006,7 +34006,7 @@
       </c>
       <c r="L454" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-02</t>
+          <t>ÉNFASIS 7°-2</t>
         </is>
       </c>
       <c r="M454" t="inlineStr">
@@ -34079,7 +34079,7 @@
       </c>
       <c r="L455" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-02</t>
+          <t>ÉNFASIS 7°-2</t>
         </is>
       </c>
       <c r="M455" t="inlineStr">
@@ -34152,7 +34152,7 @@
       </c>
       <c r="L456" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-03</t>
+          <t>ÉNFASIS 7°-3</t>
         </is>
       </c>
       <c r="M456" t="inlineStr">
@@ -34225,7 +34225,7 @@
       </c>
       <c r="L457" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-03</t>
+          <t>ÉNFASIS 7°-3</t>
         </is>
       </c>
       <c r="M457" t="inlineStr">
@@ -34298,7 +34298,7 @@
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M458" t="inlineStr">
@@ -34371,7 +34371,7 @@
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M459" t="inlineStr">
@@ -34444,7 +34444,7 @@
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M460" t="inlineStr">
@@ -34517,7 +34517,7 @@
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M461" t="inlineStr">
@@ -34582,7 +34582,7 @@
       <c r="K462" t="inlineStr"/>
       <c r="L462" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M462" t="inlineStr"/>
@@ -34643,7 +34643,7 @@
       <c r="K463" t="inlineStr"/>
       <c r="L463" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M463" t="inlineStr"/>
@@ -34704,7 +34704,7 @@
       <c r="K464" t="inlineStr"/>
       <c r="L464" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M464" t="inlineStr"/>
@@ -34765,7 +34765,7 @@
       <c r="K465" t="inlineStr"/>
       <c r="L465" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M465" t="inlineStr"/>
@@ -34826,7 +34826,7 @@
       <c r="K466" t="inlineStr"/>
       <c r="L466" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M466" t="inlineStr"/>
@@ -34887,7 +34887,7 @@
       <c r="K467" t="inlineStr"/>
       <c r="L467" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M467" t="inlineStr"/>
@@ -34952,7 +34952,7 @@
       <c r="K468" t="inlineStr"/>
       <c r="L468" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M468" t="inlineStr">
@@ -35017,7 +35017,7 @@
       <c r="K469" t="inlineStr"/>
       <c r="L469" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M469" t="inlineStr"/>
@@ -35078,7 +35078,7 @@
       <c r="K470" t="inlineStr"/>
       <c r="L470" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M470" t="inlineStr"/>
@@ -35139,7 +35139,7 @@
       <c r="K471" t="inlineStr"/>
       <c r="L471" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M471" t="inlineStr"/>
@@ -35200,7 +35200,7 @@
       <c r="K472" t="inlineStr"/>
       <c r="L472" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M472" t="inlineStr"/>
@@ -35261,7 +35261,7 @@
       <c r="K473" t="inlineStr"/>
       <c r="L473" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M473" t="inlineStr"/>
@@ -35322,7 +35322,7 @@
       <c r="K474" t="inlineStr"/>
       <c r="L474" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M474" t="inlineStr"/>
@@ -35387,7 +35387,7 @@
       <c r="K475" t="inlineStr"/>
       <c r="L475" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M475" t="inlineStr">
@@ -35456,7 +35456,7 @@
       <c r="K476" t="inlineStr"/>
       <c r="L476" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M476" t="inlineStr">
@@ -35529,7 +35529,7 @@
       </c>
       <c r="L477" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M477" t="inlineStr">
@@ -35602,7 +35602,7 @@
       </c>
       <c r="L478" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M478" t="inlineStr">
@@ -35675,7 +35675,7 @@
       </c>
       <c r="L479" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M479" t="inlineStr">
@@ -35748,7 +35748,7 @@
       </c>
       <c r="L480" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M480" t="inlineStr">
@@ -35821,7 +35821,7 @@
       </c>
       <c r="L481" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M481" t="inlineStr">
@@ -35894,7 +35894,7 @@
       </c>
       <c r="L482" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M482" t="inlineStr">
@@ -35967,7 +35967,7 @@
       </c>
       <c r="L483" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M483" t="inlineStr">
@@ -36040,7 +36040,7 @@
       </c>
       <c r="L484" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M484" t="inlineStr">
@@ -36113,7 +36113,7 @@
       </c>
       <c r="L485" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M485" t="inlineStr">
@@ -36186,7 +36186,7 @@
       </c>
       <c r="L486" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M486" t="inlineStr">
@@ -36259,7 +36259,7 @@
       </c>
       <c r="L487" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M487" t="inlineStr">
@@ -36332,7 +36332,7 @@
       </c>
       <c r="L488" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M488" t="inlineStr">
@@ -36397,7 +36397,7 @@
       <c r="K489" t="inlineStr"/>
       <c r="L489" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M489" t="inlineStr"/>
@@ -36458,7 +36458,7 @@
       <c r="K490" t="inlineStr"/>
       <c r="L490" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M490" t="inlineStr"/>
@@ -36519,7 +36519,7 @@
       <c r="K491" t="inlineStr"/>
       <c r="L491" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M491" t="inlineStr"/>
@@ -36580,7 +36580,7 @@
       <c r="K492" t="inlineStr"/>
       <c r="L492" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M492" t="inlineStr"/>
@@ -36641,7 +36641,7 @@
       <c r="K493" t="inlineStr"/>
       <c r="L493" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M493" t="inlineStr"/>
@@ -36702,7 +36702,7 @@
       <c r="K494" t="inlineStr"/>
       <c r="L494" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M494" t="inlineStr"/>
@@ -36767,7 +36767,7 @@
       <c r="K495" t="inlineStr"/>
       <c r="L495" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M495" t="inlineStr">
@@ -36832,7 +36832,7 @@
       <c r="K496" t="inlineStr"/>
       <c r="L496" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M496" t="inlineStr"/>
@@ -36893,7 +36893,7 @@
       <c r="K497" t="inlineStr"/>
       <c r="L497" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M497" t="inlineStr"/>
@@ -36954,7 +36954,7 @@
       <c r="K498" t="inlineStr"/>
       <c r="L498" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M498" t="inlineStr"/>
@@ -37015,7 +37015,7 @@
       <c r="K499" t="inlineStr"/>
       <c r="L499" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M499" t="inlineStr"/>
@@ -37076,7 +37076,7 @@
       <c r="K500" t="inlineStr"/>
       <c r="L500" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M500" t="inlineStr"/>
@@ -37137,7 +37137,7 @@
       <c r="K501" t="inlineStr"/>
       <c r="L501" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M501" t="inlineStr"/>
@@ -37202,7 +37202,7 @@
       <c r="K502" t="inlineStr"/>
       <c r="L502" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M502" t="inlineStr">
@@ -37271,7 +37271,7 @@
       <c r="K503" t="inlineStr"/>
       <c r="L503" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M503" t="inlineStr">
@@ -37344,7 +37344,7 @@
       </c>
       <c r="L504" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M504" t="inlineStr">
@@ -37417,7 +37417,7 @@
       </c>
       <c r="L505" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M505" t="inlineStr">
@@ -37490,7 +37490,7 @@
       </c>
       <c r="L506" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M506" t="inlineStr">
@@ -37563,7 +37563,7 @@
       </c>
       <c r="L507" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M507" t="inlineStr">
@@ -37636,7 +37636,7 @@
       </c>
       <c r="L508" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M508" t="inlineStr">
@@ -37709,7 +37709,7 @@
       </c>
       <c r="L509" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M509" t="inlineStr">
@@ -37782,7 +37782,7 @@
       </c>
       <c r="L510" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M510" t="inlineStr">
@@ -37855,7 +37855,7 @@
       </c>
       <c r="L511" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M511" t="inlineStr">
@@ -37928,7 +37928,7 @@
       </c>
       <c r="L512" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M512" t="inlineStr">
@@ -38001,7 +38001,7 @@
       </c>
       <c r="L513" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M513" t="inlineStr">
@@ -38074,7 +38074,7 @@
       </c>
       <c r="L514" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M514" t="inlineStr">
@@ -38147,7 +38147,7 @@
       </c>
       <c r="L515" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M515" t="inlineStr">
@@ -38216,7 +38216,7 @@
       <c r="K516" t="inlineStr"/>
       <c r="L516" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M516" t="inlineStr">
@@ -38285,7 +38285,7 @@
       <c r="K517" t="inlineStr"/>
       <c r="L517" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M517" t="inlineStr">
@@ -38354,7 +38354,7 @@
       <c r="K518" t="inlineStr"/>
       <c r="L518" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M518" t="inlineStr">
@@ -38419,7 +38419,7 @@
       <c r="K519" t="inlineStr"/>
       <c r="L519" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M519" t="inlineStr"/>
@@ -38480,7 +38480,7 @@
       <c r="K520" t="inlineStr"/>
       <c r="L520" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M520" t="inlineStr"/>
@@ -38541,7 +38541,7 @@
       <c r="K521" t="inlineStr"/>
       <c r="L521" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M521" t="inlineStr"/>
@@ -38602,7 +38602,7 @@
       <c r="K522" t="inlineStr"/>
       <c r="L522" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M522" t="inlineStr"/>
@@ -38663,7 +38663,7 @@
       <c r="K523" t="inlineStr"/>
       <c r="L523" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M523" t="inlineStr"/>
@@ -38724,7 +38724,7 @@
       <c r="K524" t="inlineStr"/>
       <c r="L524" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M524" t="inlineStr"/>
@@ -38785,7 +38785,7 @@
       <c r="K525" t="inlineStr"/>
       <c r="L525" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M525" t="inlineStr"/>
@@ -38846,7 +38846,7 @@
       <c r="K526" t="inlineStr"/>
       <c r="L526" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M526" t="inlineStr"/>
@@ -38907,7 +38907,7 @@
       <c r="K527" t="inlineStr"/>
       <c r="L527" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M527" t="inlineStr"/>
@@ -38968,7 +38968,7 @@
       <c r="K528" t="inlineStr"/>
       <c r="L528" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M528" t="inlineStr"/>
@@ -39029,7 +39029,7 @@
       <c r="K529" t="inlineStr"/>
       <c r="L529" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M529" t="inlineStr"/>
@@ -39090,7 +39090,7 @@
       <c r="K530" t="inlineStr"/>
       <c r="L530" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M530" t="inlineStr"/>
@@ -39159,7 +39159,7 @@
       </c>
       <c r="L531" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-04</t>
+          <t>ÉNFASIS 7°-4</t>
         </is>
       </c>
       <c r="M531" t="inlineStr">
@@ -39232,7 +39232,7 @@
       </c>
       <c r="L532" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-04</t>
+          <t>ÉNFASIS 7°-4</t>
         </is>
       </c>
       <c r="M532" t="inlineStr">
@@ -39305,7 +39305,7 @@
       </c>
       <c r="L533" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M533" t="inlineStr">
@@ -39378,7 +39378,7 @@
       </c>
       <c r="L534" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M534" t="inlineStr">
@@ -39451,7 +39451,7 @@
       </c>
       <c r="L535" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M535" t="inlineStr">
@@ -39524,7 +39524,7 @@
       </c>
       <c r="L536" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M536" t="inlineStr">
@@ -39597,7 +39597,7 @@
       </c>
       <c r="L537" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M537" t="inlineStr">
@@ -39670,7 +39670,7 @@
       </c>
       <c r="L538" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M538" t="inlineStr">
@@ -39743,7 +39743,7 @@
       </c>
       <c r="L539" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M539" t="inlineStr">
@@ -39816,7 +39816,7 @@
       </c>
       <c r="L540" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M540" t="inlineStr">
@@ -39885,7 +39885,7 @@
       <c r="K541" t="inlineStr"/>
       <c r="L541" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M541" t="inlineStr">
@@ -39954,7 +39954,7 @@
       <c r="K542" t="inlineStr"/>
       <c r="L542" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M542" t="inlineStr">
@@ -40023,7 +40023,7 @@
       <c r="K543" t="inlineStr"/>
       <c r="L543" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M543" t="inlineStr">
@@ -40088,7 +40088,7 @@
       <c r="K544" t="inlineStr"/>
       <c r="L544" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M544" t="inlineStr"/>
@@ -40149,7 +40149,7 @@
       <c r="K545" t="inlineStr"/>
       <c r="L545" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M545" t="inlineStr"/>
@@ -40210,7 +40210,7 @@
       <c r="K546" t="inlineStr"/>
       <c r="L546" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M546" t="inlineStr"/>
@@ -40271,7 +40271,7 @@
       <c r="K547" t="inlineStr"/>
       <c r="L547" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M547" t="inlineStr"/>
@@ -40332,7 +40332,7 @@
       <c r="K548" t="inlineStr"/>
       <c r="L548" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M548" t="inlineStr"/>
@@ -40393,7 +40393,7 @@
       <c r="K549" t="inlineStr"/>
       <c r="L549" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M549" t="inlineStr"/>
@@ -40454,7 +40454,7 @@
       <c r="K550" t="inlineStr"/>
       <c r="L550" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M550" t="inlineStr"/>
@@ -40515,7 +40515,7 @@
       <c r="K551" t="inlineStr"/>
       <c r="L551" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M551" t="inlineStr"/>
@@ -40576,7 +40576,7 @@
       <c r="K552" t="inlineStr"/>
       <c r="L552" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M552" t="inlineStr"/>
@@ -40637,7 +40637,7 @@
       <c r="K553" t="inlineStr"/>
       <c r="L553" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M553" t="inlineStr"/>
@@ -40698,7 +40698,7 @@
       <c r="K554" t="inlineStr"/>
       <c r="L554" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M554" t="inlineStr"/>
@@ -40759,7 +40759,7 @@
       <c r="K555" t="inlineStr"/>
       <c r="L555" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M555" t="inlineStr"/>
@@ -40828,7 +40828,7 @@
       </c>
       <c r="L556" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-04</t>
+          <t>ÉNFASIS 7°-4</t>
         </is>
       </c>
       <c r="M556" t="inlineStr">
@@ -40901,7 +40901,7 @@
       </c>
       <c r="L557" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-04</t>
+          <t>ÉNFASIS 7°-4</t>
         </is>
       </c>
       <c r="M557" t="inlineStr">
@@ -40974,7 +40974,7 @@
       </c>
       <c r="L558" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M558" t="inlineStr">
@@ -41047,7 +41047,7 @@
       </c>
       <c r="L559" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M559" t="inlineStr">
@@ -41120,7 +41120,7 @@
       </c>
       <c r="L560" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M560" t="inlineStr">
@@ -41193,7 +41193,7 @@
       </c>
       <c r="L561" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M561" t="inlineStr">
@@ -41266,7 +41266,7 @@
       </c>
       <c r="L562" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M562" t="inlineStr">
@@ -41339,7 +41339,7 @@
       </c>
       <c r="L563" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M563" t="inlineStr">
@@ -41412,7 +41412,7 @@
       </c>
       <c r="L564" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M564" t="inlineStr">
@@ -41485,7 +41485,7 @@
       </c>
       <c r="L565" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M565" t="inlineStr">
@@ -41554,7 +41554,7 @@
       <c r="K566" t="inlineStr"/>
       <c r="L566" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M566" t="inlineStr">
@@ -41623,7 +41623,7 @@
       <c r="K567" t="inlineStr"/>
       <c r="L567" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M567" t="inlineStr">
@@ -41688,7 +41688,7 @@
       <c r="K568" t="inlineStr"/>
       <c r="L568" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M568" t="inlineStr"/>
@@ -41749,7 +41749,7 @@
       <c r="K569" t="inlineStr"/>
       <c r="L569" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M569" t="inlineStr"/>
@@ -41814,7 +41814,7 @@
       <c r="K570" t="inlineStr"/>
       <c r="L570" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M570" t="inlineStr">
@@ -41879,7 +41879,7 @@
       <c r="K571" t="inlineStr"/>
       <c r="L571" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M571" t="inlineStr"/>
@@ -41944,7 +41944,7 @@
       <c r="K572" t="inlineStr"/>
       <c r="L572" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M572" t="inlineStr">
@@ -42013,7 +42013,7 @@
       <c r="K573" t="inlineStr"/>
       <c r="L573" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M573" t="inlineStr">
@@ -42078,7 +42078,7 @@
       <c r="K574" t="inlineStr"/>
       <c r="L574" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M574" t="inlineStr"/>
@@ -42139,7 +42139,7 @@
       <c r="K575" t="inlineStr"/>
       <c r="L575" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M575" t="inlineStr"/>
@@ -42204,7 +42204,7 @@
       <c r="K576" t="inlineStr"/>
       <c r="L576" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M576" t="inlineStr">
@@ -42269,7 +42269,7 @@
       <c r="K577" t="inlineStr"/>
       <c r="L577" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M577" t="inlineStr"/>
@@ -42330,7 +42330,7 @@
       <c r="K578" t="inlineStr"/>
       <c r="L578" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M578" t="inlineStr"/>
@@ -42399,7 +42399,7 @@
       </c>
       <c r="L579" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-01</t>
+          <t>ÉNFASIS 6°-1</t>
         </is>
       </c>
       <c r="M579" t="inlineStr">
@@ -42472,7 +42472,7 @@
       </c>
       <c r="L580" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-01</t>
+          <t>ÉNFASIS 6°-1</t>
         </is>
       </c>
       <c r="M580" t="inlineStr">
@@ -42545,7 +42545,7 @@
       </c>
       <c r="L581" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-02</t>
+          <t>ÉNFASIS 6°-2</t>
         </is>
       </c>
       <c r="M581" t="inlineStr">
@@ -42618,7 +42618,7 @@
       </c>
       <c r="L582" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-02</t>
+          <t>ÉNFASIS 6°-2</t>
         </is>
       </c>
       <c r="M582" t="inlineStr">
@@ -42691,7 +42691,7 @@
       </c>
       <c r="L583" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M583" t="inlineStr">
@@ -42764,7 +42764,7 @@
       </c>
       <c r="L584" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M584" t="inlineStr">
@@ -42837,7 +42837,7 @@
       </c>
       <c r="L585" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M585" t="inlineStr">
@@ -42910,7 +42910,7 @@
       </c>
       <c r="L586" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M586" t="inlineStr">
@@ -42983,7 +42983,7 @@
       </c>
       <c r="L587" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M587" t="inlineStr">
@@ -43056,7 +43056,7 @@
       </c>
       <c r="L588" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M588" t="inlineStr">
@@ -43129,7 +43129,7 @@
       </c>
       <c r="L589" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M589" t="inlineStr">
@@ -43202,7 +43202,7 @@
       </c>
       <c r="L590" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M590" t="inlineStr">
@@ -43275,7 +43275,7 @@
       </c>
       <c r="L591" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M591" t="inlineStr">
@@ -43348,7 +43348,7 @@
       </c>
       <c r="L592" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M592" t="inlineStr">
@@ -43421,7 +43421,7 @@
       </c>
       <c r="L593" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M593" t="inlineStr">
@@ -43494,7 +43494,7 @@
       </c>
       <c r="L594" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M594" t="inlineStr">
@@ -43563,7 +43563,7 @@
       <c r="K595" t="inlineStr"/>
       <c r="L595" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M595" t="inlineStr">
@@ -43632,7 +43632,7 @@
       <c r="K596" t="inlineStr"/>
       <c r="L596" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M596" t="inlineStr">
@@ -43697,7 +43697,7 @@
       <c r="K597" t="inlineStr"/>
       <c r="L597" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M597" t="inlineStr"/>
@@ -43758,7 +43758,7 @@
       <c r="K598" t="inlineStr"/>
       <c r="L598" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M598" t="inlineStr"/>
@@ -43823,7 +43823,7 @@
       <c r="K599" t="inlineStr"/>
       <c r="L599" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M599" t="inlineStr">
@@ -43888,7 +43888,7 @@
       <c r="K600" t="inlineStr"/>
       <c r="L600" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M600" t="inlineStr"/>
@@ -43953,7 +43953,7 @@
       <c r="K601" t="inlineStr"/>
       <c r="L601" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M601" t="inlineStr">
@@ -44022,7 +44022,7 @@
       <c r="K602" t="inlineStr"/>
       <c r="L602" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M602" t="inlineStr">
@@ -44087,7 +44087,7 @@
       <c r="K603" t="inlineStr"/>
       <c r="L603" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M603" t="inlineStr"/>
@@ -44148,7 +44148,7 @@
       <c r="K604" t="inlineStr"/>
       <c r="L604" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M604" t="inlineStr"/>
@@ -44213,7 +44213,7 @@
       <c r="K605" t="inlineStr"/>
       <c r="L605" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M605" t="inlineStr">
@@ -44278,7 +44278,7 @@
       <c r="K606" t="inlineStr"/>
       <c r="L606" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M606" t="inlineStr"/>
@@ -44339,7 +44339,7 @@
       <c r="K607" t="inlineStr"/>
       <c r="L607" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M607" t="inlineStr"/>
@@ -44408,7 +44408,7 @@
       </c>
       <c r="L608" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-01</t>
+          <t>ÉNFASIS 6°-1</t>
         </is>
       </c>
       <c r="M608" t="inlineStr">
@@ -44481,7 +44481,7 @@
       </c>
       <c r="L609" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-01</t>
+          <t>ÉNFASIS 6°-1</t>
         </is>
       </c>
       <c r="M609" t="inlineStr">
@@ -44554,7 +44554,7 @@
       </c>
       <c r="L610" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-02</t>
+          <t>ÉNFASIS 6°-2</t>
         </is>
       </c>
       <c r="M610" t="inlineStr">
@@ -44627,7 +44627,7 @@
       </c>
       <c r="L611" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-02</t>
+          <t>ÉNFASIS 6°-2</t>
         </is>
       </c>
       <c r="M611" t="inlineStr">
@@ -44700,7 +44700,7 @@
       </c>
       <c r="L612" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M612" t="inlineStr">
@@ -44773,7 +44773,7 @@
       </c>
       <c r="L613" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M613" t="inlineStr">
@@ -44846,7 +44846,7 @@
       </c>
       <c r="L614" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M614" t="inlineStr">
@@ -44919,7 +44919,7 @@
       </c>
       <c r="L615" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-01</t>
+          <t>ÉNFASIS 9°-1</t>
         </is>
       </c>
       <c r="M615" t="inlineStr">
@@ -44992,7 +44992,7 @@
       </c>
       <c r="L616" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M616" t="inlineStr">
@@ -45065,7 +45065,7 @@
       </c>
       <c r="L617" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M617" t="inlineStr">
@@ -45138,7 +45138,7 @@
       </c>
       <c r="L618" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M618" t="inlineStr">
@@ -45211,7 +45211,7 @@
       </c>
       <c r="L619" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M619" t="inlineStr">
@@ -45284,7 +45284,7 @@
       </c>
       <c r="L620" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M620" t="inlineStr">
@@ -45357,7 +45357,7 @@
       </c>
       <c r="L621" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M621" t="inlineStr">
@@ -45430,7 +45430,7 @@
       </c>
       <c r="L622" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M622" t="inlineStr">
@@ -45503,7 +45503,7 @@
       </c>
       <c r="L623" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M623" t="inlineStr">
@@ -45568,7 +45568,7 @@
       <c r="K624" t="inlineStr"/>
       <c r="L624" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M624" t="inlineStr"/>
@@ -45629,7 +45629,7 @@
       <c r="K625" t="inlineStr"/>
       <c r="L625" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M625" t="inlineStr"/>
@@ -45690,7 +45690,7 @@
       <c r="K626" t="inlineStr"/>
       <c r="L626" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M626" t="inlineStr"/>
@@ -45751,7 +45751,7 @@
       <c r="K627" t="inlineStr"/>
       <c r="L627" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M627" t="inlineStr"/>
@@ -45816,7 +45816,7 @@
       <c r="K628" t="inlineStr"/>
       <c r="L628" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M628" t="inlineStr">
@@ -45881,7 +45881,7 @@
       <c r="K629" t="inlineStr"/>
       <c r="L629" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M629" t="inlineStr"/>
@@ -45942,7 +45942,7 @@
       <c r="K630" t="inlineStr"/>
       <c r="L630" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M630" t="inlineStr"/>
@@ -46003,7 +46003,7 @@
       <c r="K631" t="inlineStr"/>
       <c r="L631" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M631" t="inlineStr"/>
@@ -46064,7 +46064,7 @@
       <c r="K632" t="inlineStr"/>
       <c r="L632" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M632" t="inlineStr"/>
@@ -46125,7 +46125,7 @@
       <c r="K633" t="inlineStr"/>
       <c r="L633" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M633" t="inlineStr"/>
@@ -46186,7 +46186,7 @@
       <c r="K634" t="inlineStr"/>
       <c r="L634" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M634" t="inlineStr"/>
@@ -46251,7 +46251,7 @@
       <c r="K635" t="inlineStr"/>
       <c r="L635" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M635" t="inlineStr">
@@ -46324,7 +46324,7 @@
       </c>
       <c r="L636" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-01</t>
+          <t>ÉNFASIS 7°-1</t>
         </is>
       </c>
       <c r="M636" t="inlineStr">
@@ -46397,7 +46397,7 @@
       </c>
       <c r="L637" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-01</t>
+          <t>ÉNFASIS 7°-1</t>
         </is>
       </c>
       <c r="M637" t="inlineStr">
@@ -46470,7 +46470,7 @@
       </c>
       <c r="L638" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-02</t>
+          <t>ÉNFASIS 7°-2</t>
         </is>
       </c>
       <c r="M638" t="inlineStr">
@@ -46543,7 +46543,7 @@
       </c>
       <c r="L639" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-02</t>
+          <t>ÉNFASIS 7°-2</t>
         </is>
       </c>
       <c r="M639" t="inlineStr">
@@ -46616,7 +46616,7 @@
       </c>
       <c r="L640" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-03</t>
+          <t>ÉNFASIS 7°-3</t>
         </is>
       </c>
       <c r="M640" t="inlineStr">
@@ -46689,7 +46689,7 @@
       </c>
       <c r="L641" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-03</t>
+          <t>ÉNFASIS 7°-3</t>
         </is>
       </c>
       <c r="M641" t="inlineStr">
@@ -46762,7 +46762,7 @@
       </c>
       <c r="L642" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M642" t="inlineStr">
@@ -46835,7 +46835,7 @@
       </c>
       <c r="L643" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M643" t="inlineStr">
@@ -46908,7 +46908,7 @@
       </c>
       <c r="L644" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M644" t="inlineStr">
@@ -46981,7 +46981,7 @@
       </c>
       <c r="L645" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M645" t="inlineStr">
@@ -47054,7 +47054,7 @@
       </c>
       <c r="L646" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M646" t="inlineStr">
@@ -47127,7 +47127,7 @@
       </c>
       <c r="L647" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M647" t="inlineStr">
@@ -47200,7 +47200,7 @@
       </c>
       <c r="L648" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M648" t="inlineStr">
@@ -47273,7 +47273,7 @@
       </c>
       <c r="L649" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M649" t="inlineStr">
@@ -47338,7 +47338,7 @@
       <c r="K650" t="inlineStr"/>
       <c r="L650" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M650" t="inlineStr"/>
@@ -47399,7 +47399,7 @@
       <c r="K651" t="inlineStr"/>
       <c r="L651" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M651" t="inlineStr"/>
@@ -47460,7 +47460,7 @@
       <c r="K652" t="inlineStr"/>
       <c r="L652" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M652" t="inlineStr"/>
@@ -47521,7 +47521,7 @@
       <c r="K653" t="inlineStr"/>
       <c r="L653" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M653" t="inlineStr"/>
@@ -47586,7 +47586,7 @@
       <c r="K654" t="inlineStr"/>
       <c r="L654" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M654" t="inlineStr">
@@ -47651,7 +47651,7 @@
       <c r="K655" t="inlineStr"/>
       <c r="L655" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M655" t="inlineStr"/>
@@ -47712,7 +47712,7 @@
       <c r="K656" t="inlineStr"/>
       <c r="L656" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M656" t="inlineStr"/>
@@ -47773,7 +47773,7 @@
       <c r="K657" t="inlineStr"/>
       <c r="L657" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M657" t="inlineStr"/>
@@ -47834,7 +47834,7 @@
       <c r="K658" t="inlineStr"/>
       <c r="L658" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M658" t="inlineStr"/>
@@ -47895,7 +47895,7 @@
       <c r="K659" t="inlineStr"/>
       <c r="L659" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M659" t="inlineStr"/>
@@ -47956,7 +47956,7 @@
       <c r="K660" t="inlineStr"/>
       <c r="L660" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M660" t="inlineStr"/>
@@ -48021,7 +48021,7 @@
       <c r="K661" t="inlineStr"/>
       <c r="L661" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M661" t="inlineStr">
@@ -48094,7 +48094,7 @@
       </c>
       <c r="L662" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-01</t>
+          <t>ÉNFASIS 7°-1</t>
         </is>
       </c>
       <c r="M662" t="inlineStr">
@@ -48167,7 +48167,7 @@
       </c>
       <c r="L663" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-01</t>
+          <t>ÉNFASIS 7°-1</t>
         </is>
       </c>
       <c r="M663" t="inlineStr">
@@ -48240,7 +48240,7 @@
       </c>
       <c r="L664" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-02</t>
+          <t>ÉNFASIS 7°-2</t>
         </is>
       </c>
       <c r="M664" t="inlineStr">
@@ -48313,7 +48313,7 @@
       </c>
       <c r="L665" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-02</t>
+          <t>ÉNFASIS 7°-2</t>
         </is>
       </c>
       <c r="M665" t="inlineStr">
@@ -48386,7 +48386,7 @@
       </c>
       <c r="L666" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-03</t>
+          <t>ÉNFASIS 7°-3</t>
         </is>
       </c>
       <c r="M666" t="inlineStr">
@@ -48459,7 +48459,7 @@
       </c>
       <c r="L667" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-03</t>
+          <t>ÉNFASIS 7°-3</t>
         </is>
       </c>
       <c r="M667" t="inlineStr">
@@ -48532,7 +48532,7 @@
       </c>
       <c r="L668" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M668" t="inlineStr">
@@ -48605,7 +48605,7 @@
       </c>
       <c r="L669" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M669" t="inlineStr">
@@ -48678,7 +48678,7 @@
       </c>
       <c r="L670" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M670" t="inlineStr">
@@ -48751,7 +48751,7 @@
       </c>
       <c r="L671" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M671" t="inlineStr">
@@ -48824,7 +48824,7 @@
       </c>
       <c r="L672" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M672" t="inlineStr">
@@ -48897,7 +48897,7 @@
       </c>
       <c r="L673" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M673" t="inlineStr">
@@ -48970,7 +48970,7 @@
       </c>
       <c r="L674" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M674" t="inlineStr">
@@ -49043,7 +49043,7 @@
       </c>
       <c r="L675" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M675" t="inlineStr">
@@ -49108,7 +49108,7 @@
       <c r="K676" t="inlineStr"/>
       <c r="L676" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M676" t="inlineStr"/>
@@ -49173,7 +49173,7 @@
       <c r="K677" t="inlineStr"/>
       <c r="L677" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M677" t="inlineStr">
@@ -49238,7 +49238,7 @@
       <c r="K678" t="inlineStr"/>
       <c r="L678" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M678" t="inlineStr"/>
@@ -49299,7 +49299,7 @@
       <c r="K679" t="inlineStr"/>
       <c r="L679" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M679" t="inlineStr"/>
@@ -49364,7 +49364,7 @@
       <c r="K680" t="inlineStr"/>
       <c r="L680" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M680" t="inlineStr">
@@ -49433,7 +49433,7 @@
       <c r="K681" t="inlineStr"/>
       <c r="L681" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M681" t="inlineStr">
@@ -49498,7 +49498,7 @@
       <c r="K682" t="inlineStr"/>
       <c r="L682" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M682" t="inlineStr"/>
@@ -49559,7 +49559,7 @@
       <c r="K683" t="inlineStr"/>
       <c r="L683" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M683" t="inlineStr"/>
@@ -49620,7 +49620,7 @@
       <c r="K684" t="inlineStr"/>
       <c r="L684" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M684" t="inlineStr"/>
@@ -49681,7 +49681,7 @@
       <c r="K685" t="inlineStr"/>
       <c r="L685" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M685" t="inlineStr"/>
@@ -49746,7 +49746,7 @@
       <c r="K686" t="inlineStr"/>
       <c r="L686" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M686" t="inlineStr">
@@ -49815,7 +49815,7 @@
       <c r="K687" t="inlineStr"/>
       <c r="L687" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M687" t="inlineStr">
@@ -49880,7 +49880,7 @@
       <c r="K688" t="inlineStr"/>
       <c r="L688" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M688" t="inlineStr"/>
@@ -49941,7 +49941,7 @@
       <c r="K689" t="inlineStr"/>
       <c r="L689" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M689" t="inlineStr"/>
@@ -50002,7 +50002,7 @@
       <c r="K690" t="inlineStr"/>
       <c r="L690" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M690" t="inlineStr"/>
@@ -50067,7 +50067,7 @@
       <c r="K691" t="inlineStr"/>
       <c r="L691" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M691" t="inlineStr">
@@ -50132,7 +50132,7 @@
       <c r="K692" t="inlineStr"/>
       <c r="L692" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M692" t="inlineStr"/>
@@ -50201,7 +50201,7 @@
       </c>
       <c r="L693" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M693" t="inlineStr">
@@ -50274,7 +50274,7 @@
       </c>
       <c r="L694" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M694" t="inlineStr">
@@ -50347,7 +50347,7 @@
       </c>
       <c r="L695" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M695" t="inlineStr">
@@ -50420,7 +50420,7 @@
       </c>
       <c r="L696" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M696" t="inlineStr">
@@ -50485,7 +50485,7 @@
       <c r="K697" t="inlineStr"/>
       <c r="L697" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M697" t="inlineStr"/>
@@ -50550,7 +50550,7 @@
       <c r="K698" t="inlineStr"/>
       <c r="L698" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M698" t="inlineStr">
@@ -50615,7 +50615,7 @@
       <c r="K699" t="inlineStr"/>
       <c r="L699" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M699" t="inlineStr"/>
@@ -50676,7 +50676,7 @@
       <c r="K700" t="inlineStr"/>
       <c r="L700" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M700" t="inlineStr"/>
@@ -50741,7 +50741,7 @@
       <c r="K701" t="inlineStr"/>
       <c r="L701" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M701" t="inlineStr">
@@ -50810,7 +50810,7 @@
       <c r="K702" t="inlineStr"/>
       <c r="L702" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M702" t="inlineStr">
@@ -50875,7 +50875,7 @@
       <c r="K703" t="inlineStr"/>
       <c r="L703" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M703" t="inlineStr"/>
@@ -50936,7 +50936,7 @@
       <c r="K704" t="inlineStr"/>
       <c r="L704" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M704" t="inlineStr"/>
@@ -50997,7 +50997,7 @@
       <c r="K705" t="inlineStr"/>
       <c r="L705" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M705" t="inlineStr"/>
@@ -51058,7 +51058,7 @@
       <c r="K706" t="inlineStr"/>
       <c r="L706" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M706" t="inlineStr"/>
@@ -51123,7 +51123,7 @@
       <c r="K707" t="inlineStr"/>
       <c r="L707" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M707" t="inlineStr">
@@ -51192,7 +51192,7 @@
       <c r="K708" t="inlineStr"/>
       <c r="L708" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M708" t="inlineStr">
@@ -51257,7 +51257,7 @@
       <c r="K709" t="inlineStr"/>
       <c r="L709" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M709" t="inlineStr"/>
@@ -51318,7 +51318,7 @@
       <c r="K710" t="inlineStr"/>
       <c r="L710" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M710" t="inlineStr"/>
@@ -51379,7 +51379,7 @@
       <c r="K711" t="inlineStr"/>
       <c r="L711" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M711" t="inlineStr"/>
@@ -51444,7 +51444,7 @@
       <c r="K712" t="inlineStr"/>
       <c r="L712" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M712" t="inlineStr">
@@ -51509,7 +51509,7 @@
       <c r="K713" t="inlineStr"/>
       <c r="L713" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M713" t="inlineStr"/>
@@ -51578,7 +51578,7 @@
       </c>
       <c r="L714" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M714" t="inlineStr">
@@ -51651,7 +51651,7 @@
       </c>
       <c r="L715" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M715" t="inlineStr">
@@ -51724,7 +51724,7 @@
       </c>
       <c r="L716" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M716" t="inlineStr">
@@ -51797,7 +51797,7 @@
       </c>
       <c r="L717" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-01</t>
+          <t>ÉNFASIS 11°-1</t>
         </is>
       </c>
       <c r="M717" t="inlineStr">
@@ -51866,7 +51866,7 @@
       <c r="K718" t="inlineStr"/>
       <c r="L718" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M718" t="inlineStr">
@@ -51931,7 +51931,7 @@
       <c r="K719" t="inlineStr"/>
       <c r="L719" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M719" t="inlineStr"/>
@@ -51992,7 +51992,7 @@
       <c r="K720" t="inlineStr"/>
       <c r="L720" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M720" t="inlineStr"/>
@@ -52053,7 +52053,7 @@
       <c r="K721" t="inlineStr"/>
       <c r="L721" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M721" t="inlineStr"/>
@@ -52114,7 +52114,7 @@
       <c r="K722" t="inlineStr"/>
       <c r="L722" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M722" t="inlineStr"/>
@@ -52179,7 +52179,7 @@
       <c r="K723" t="inlineStr"/>
       <c r="L723" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M723" t="inlineStr">
@@ -52244,7 +52244,7 @@
       <c r="K724" t="inlineStr"/>
       <c r="L724" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M724" t="inlineStr"/>
@@ -52305,7 +52305,7 @@
       <c r="K725" t="inlineStr"/>
       <c r="L725" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M725" t="inlineStr"/>
@@ -52366,7 +52366,7 @@
       <c r="K726" t="inlineStr"/>
       <c r="L726" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M726" t="inlineStr"/>
@@ -52427,7 +52427,7 @@
       <c r="K727" t="inlineStr"/>
       <c r="L727" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M727" t="inlineStr"/>
@@ -52488,7 +52488,7 @@
       <c r="K728" t="inlineStr"/>
       <c r="L728" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M728" t="inlineStr"/>
@@ -52549,7 +52549,7 @@
       <c r="K729" t="inlineStr"/>
       <c r="L729" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M729" t="inlineStr"/>
@@ -52610,7 +52610,7 @@
       <c r="K730" t="inlineStr"/>
       <c r="L730" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M730" t="inlineStr"/>
@@ -52675,7 +52675,7 @@
       <c r="K731" t="inlineStr"/>
       <c r="L731" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M731" t="inlineStr">
@@ -52748,7 +52748,7 @@
       </c>
       <c r="L732" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-04</t>
+          <t>ÉNFASIS 7°-4</t>
         </is>
       </c>
       <c r="M732" t="inlineStr">
@@ -52821,7 +52821,7 @@
       </c>
       <c r="L733" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-04</t>
+          <t>ÉNFASIS 7°-4</t>
         </is>
       </c>
       <c r="M733" t="inlineStr">
@@ -52894,7 +52894,7 @@
       </c>
       <c r="L734" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M734" t="inlineStr">
@@ -52967,7 +52967,7 @@
       </c>
       <c r="L735" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M735" t="inlineStr">
@@ -53040,7 +53040,7 @@
       </c>
       <c r="L736" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M736" t="inlineStr">
@@ -53113,7 +53113,7 @@
       </c>
       <c r="L737" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M737" t="inlineStr">
@@ -53186,7 +53186,7 @@
       </c>
       <c r="L738" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M738" t="inlineStr">
@@ -53259,7 +53259,7 @@
       </c>
       <c r="L739" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M739" t="inlineStr">
@@ -53332,7 +53332,7 @@
       </c>
       <c r="L740" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M740" t="inlineStr">
@@ -53405,7 +53405,7 @@
       </c>
       <c r="L741" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M741" t="inlineStr">
@@ -53478,7 +53478,7 @@
       </c>
       <c r="L742" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M742" t="inlineStr">
@@ -53551,7 +53551,7 @@
       </c>
       <c r="L743" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M743" t="inlineStr">
@@ -53624,7 +53624,7 @@
       </c>
       <c r="L744" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M744" t="inlineStr">
@@ -53697,7 +53697,7 @@
       </c>
       <c r="L745" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M745" t="inlineStr">
@@ -53766,7 +53766,7 @@
       <c r="K746" t="inlineStr"/>
       <c r="L746" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M746" t="inlineStr">
@@ -53831,7 +53831,7 @@
       <c r="K747" t="inlineStr"/>
       <c r="L747" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M747" t="inlineStr"/>
@@ -53892,7 +53892,7 @@
       <c r="K748" t="inlineStr"/>
       <c r="L748" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M748" t="inlineStr"/>
@@ -53953,7 +53953,7 @@
       <c r="K749" t="inlineStr"/>
       <c r="L749" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M749" t="inlineStr"/>
@@ -54014,7 +54014,7 @@
       <c r="K750" t="inlineStr"/>
       <c r="L750" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M750" t="inlineStr"/>
@@ -54079,7 +54079,7 @@
       <c r="K751" t="inlineStr"/>
       <c r="L751" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M751" t="inlineStr">
@@ -54144,7 +54144,7 @@
       <c r="K752" t="inlineStr"/>
       <c r="L752" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M752" t="inlineStr"/>
@@ -54205,7 +54205,7 @@
       <c r="K753" t="inlineStr"/>
       <c r="L753" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M753" t="inlineStr"/>
@@ -54266,7 +54266,7 @@
       <c r="K754" t="inlineStr"/>
       <c r="L754" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M754" t="inlineStr"/>
@@ -54327,7 +54327,7 @@
       <c r="K755" t="inlineStr"/>
       <c r="L755" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M755" t="inlineStr"/>
@@ -54388,7 +54388,7 @@
       <c r="K756" t="inlineStr"/>
       <c r="L756" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M756" t="inlineStr"/>
@@ -54449,7 +54449,7 @@
       <c r="K757" t="inlineStr"/>
       <c r="L757" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M757" t="inlineStr"/>
@@ -54510,7 +54510,7 @@
       <c r="K758" t="inlineStr"/>
       <c r="L758" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M758" t="inlineStr"/>
@@ -54575,7 +54575,7 @@
       <c r="K759" t="inlineStr"/>
       <c r="L759" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M759" t="inlineStr">
@@ -54648,7 +54648,7 @@
       </c>
       <c r="L760" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-04</t>
+          <t>ÉNFASIS 7°-4</t>
         </is>
       </c>
       <c r="M760" t="inlineStr">
@@ -54721,7 +54721,7 @@
       </c>
       <c r="L761" t="inlineStr">
         <is>
-          <t>ÉNFASIS 7°-04</t>
+          <t>ÉNFASIS 7°-4</t>
         </is>
       </c>
       <c r="M761" t="inlineStr">
@@ -54794,7 +54794,7 @@
       </c>
       <c r="L762" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M762" t="inlineStr">
@@ -54867,7 +54867,7 @@
       </c>
       <c r="L763" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M763" t="inlineStr">
@@ -54940,7 +54940,7 @@
       </c>
       <c r="L764" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M764" t="inlineStr">
@@ -55013,7 +55013,7 @@
       </c>
       <c r="L765" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M765" t="inlineStr">
@@ -55086,7 +55086,7 @@
       </c>
       <c r="L766" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M766" t="inlineStr">
@@ -55159,7 +55159,7 @@
       </c>
       <c r="L767" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M767" t="inlineStr">
@@ -55232,7 +55232,7 @@
       </c>
       <c r="L768" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M768" t="inlineStr">
@@ -55305,7 +55305,7 @@
       </c>
       <c r="L769" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M769" t="inlineStr">
@@ -55378,7 +55378,7 @@
       </c>
       <c r="L770" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M770" t="inlineStr">
@@ -55451,7 +55451,7 @@
       </c>
       <c r="L771" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M771" t="inlineStr">
@@ -55524,7 +55524,7 @@
       </c>
       <c r="L772" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M772" t="inlineStr">
@@ -55597,7 +55597,7 @@
       </c>
       <c r="L773" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M773" t="inlineStr">
@@ -55666,7 +55666,7 @@
       <c r="K774" t="inlineStr"/>
       <c r="L774" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M774" t="inlineStr">
@@ -55735,7 +55735,7 @@
       <c r="K775" t="inlineStr"/>
       <c r="L775" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M775" t="inlineStr">
@@ -55800,7 +55800,7 @@
       <c r="K776" t="inlineStr"/>
       <c r="L776" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M776" t="inlineStr"/>
@@ -55861,7 +55861,7 @@
       <c r="K777" t="inlineStr"/>
       <c r="L777" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M777" t="inlineStr"/>
@@ -55922,7 +55922,7 @@
       <c r="K778" t="inlineStr"/>
       <c r="L778" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M778" t="inlineStr"/>
@@ -55983,7 +55983,7 @@
       <c r="K779" t="inlineStr"/>
       <c r="L779" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M779" t="inlineStr"/>
@@ -56048,7 +56048,7 @@
       <c r="K780" t="inlineStr"/>
       <c r="L780" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M780" t="inlineStr">
@@ -56113,7 +56113,7 @@
       <c r="K781" t="inlineStr"/>
       <c r="L781" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M781" t="inlineStr"/>
@@ -56174,7 +56174,7 @@
       <c r="K782" t="inlineStr"/>
       <c r="L782" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M782" t="inlineStr"/>
@@ -56235,7 +56235,7 @@
       <c r="K783" t="inlineStr"/>
       <c r="L783" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M783" t="inlineStr"/>
@@ -56296,7 +56296,7 @@
       <c r="K784" t="inlineStr"/>
       <c r="L784" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M784" t="inlineStr"/>
@@ -56361,7 +56361,7 @@
       <c r="K785" t="inlineStr"/>
       <c r="L785" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M785" t="inlineStr">
@@ -56426,7 +56426,7 @@
       <c r="K786" t="inlineStr"/>
       <c r="L786" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M786" t="inlineStr"/>
@@ -56487,7 +56487,7 @@
       <c r="K787" t="inlineStr"/>
       <c r="L787" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M787" t="inlineStr"/>
@@ -56556,7 +56556,7 @@
       </c>
       <c r="L788" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-01</t>
+          <t>ÉNFASIS 6°-1</t>
         </is>
       </c>
       <c r="M788" t="inlineStr">
@@ -56629,7 +56629,7 @@
       </c>
       <c r="L789" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-01</t>
+          <t>ÉNFASIS 6°-1</t>
         </is>
       </c>
       <c r="M789" t="inlineStr">
@@ -56702,7 +56702,7 @@
       </c>
       <c r="L790" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-02</t>
+          <t>ÉNFASIS 6°-2</t>
         </is>
       </c>
       <c r="M790" t="inlineStr">
@@ -56775,7 +56775,7 @@
       </c>
       <c r="L791" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-02</t>
+          <t>ÉNFASIS 6°-2</t>
         </is>
       </c>
       <c r="M791" t="inlineStr">
@@ -56848,7 +56848,7 @@
       </c>
       <c r="L792" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M792" t="inlineStr">
@@ -56921,7 +56921,7 @@
       </c>
       <c r="L793" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M793" t="inlineStr">
@@ -56994,7 +56994,7 @@
       </c>
       <c r="L794" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M794" t="inlineStr">
@@ -57067,7 +57067,7 @@
       </c>
       <c r="L795" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M795" t="inlineStr">
@@ -57140,7 +57140,7 @@
       </c>
       <c r="L796" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M796" t="inlineStr">
@@ -57213,7 +57213,7 @@
       </c>
       <c r="L797" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M797" t="inlineStr">
@@ -57286,7 +57286,7 @@
       </c>
       <c r="L798" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M798" t="inlineStr">
@@ -57359,7 +57359,7 @@
       </c>
       <c r="L799" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M799" t="inlineStr">
@@ -57428,7 +57428,7 @@
       <c r="K800" t="inlineStr"/>
       <c r="L800" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M800" t="inlineStr">
@@ -57497,7 +57497,7 @@
       <c r="K801" t="inlineStr"/>
       <c r="L801" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M801" t="inlineStr">
@@ -57562,7 +57562,7 @@
       <c r="K802" t="inlineStr"/>
       <c r="L802" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M802" t="inlineStr"/>
@@ -57623,7 +57623,7 @@
       <c r="K803" t="inlineStr"/>
       <c r="L803" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M803" t="inlineStr"/>
@@ -57684,7 +57684,7 @@
       <c r="K804" t="inlineStr"/>
       <c r="L804" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M804" t="inlineStr"/>
@@ -57745,7 +57745,7 @@
       <c r="K805" t="inlineStr"/>
       <c r="L805" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M805" t="inlineStr"/>
@@ -57810,7 +57810,7 @@
       <c r="K806" t="inlineStr"/>
       <c r="L806" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M806" t="inlineStr">
@@ -57875,7 +57875,7 @@
       <c r="K807" t="inlineStr"/>
       <c r="L807" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M807" t="inlineStr"/>
@@ -57936,7 +57936,7 @@
       <c r="K808" t="inlineStr"/>
       <c r="L808" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M808" t="inlineStr"/>
@@ -57997,7 +57997,7 @@
       <c r="K809" t="inlineStr"/>
       <c r="L809" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M809" t="inlineStr"/>
@@ -58058,7 +58058,7 @@
       <c r="K810" t="inlineStr"/>
       <c r="L810" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M810" t="inlineStr"/>
@@ -58123,7 +58123,7 @@
       <c r="K811" t="inlineStr"/>
       <c r="L811" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M811" t="inlineStr">
@@ -58188,7 +58188,7 @@
       <c r="K812" t="inlineStr"/>
       <c r="L812" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M812" t="inlineStr"/>
@@ -58249,7 +58249,7 @@
       <c r="K813" t="inlineStr"/>
       <c r="L813" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M813" t="inlineStr"/>
@@ -58318,7 +58318,7 @@
       </c>
       <c r="L814" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-01</t>
+          <t>ÉNFASIS 6°-1</t>
         </is>
       </c>
       <c r="M814" t="inlineStr">
@@ -58391,7 +58391,7 @@
       </c>
       <c r="L815" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-01</t>
+          <t>ÉNFASIS 6°-1</t>
         </is>
       </c>
       <c r="M815" t="inlineStr">
@@ -58464,7 +58464,7 @@
       </c>
       <c r="L816" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-02</t>
+          <t>ÉNFASIS 6°-2</t>
         </is>
       </c>
       <c r="M816" t="inlineStr">
@@ -58537,7 +58537,7 @@
       </c>
       <c r="L817" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-02</t>
+          <t>ÉNFASIS 6°-2</t>
         </is>
       </c>
       <c r="M817" t="inlineStr">
@@ -58610,7 +58610,7 @@
       </c>
       <c r="L818" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M818" t="inlineStr">
@@ -58683,7 +58683,7 @@
       </c>
       <c r="L819" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M819" t="inlineStr">
@@ -58756,7 +58756,7 @@
       </c>
       <c r="L820" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M820" t="inlineStr">
@@ -58829,7 +58829,7 @@
       </c>
       <c r="L821" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M821" t="inlineStr">
@@ -58902,7 +58902,7 @@
       </c>
       <c r="L822" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M822" t="inlineStr">
@@ -58975,7 +58975,7 @@
       </c>
       <c r="L823" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M823" t="inlineStr">
@@ -59048,7 +59048,7 @@
       </c>
       <c r="L824" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M824" t="inlineStr">
@@ -59121,7 +59121,7 @@
       </c>
       <c r="L825" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M825" t="inlineStr">
@@ -59186,7 +59186,7 @@
       <c r="K826" t="inlineStr"/>
       <c r="L826" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M826" t="inlineStr"/>
@@ -59247,7 +59247,7 @@
       <c r="K827" t="inlineStr"/>
       <c r="L827" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M827" t="inlineStr"/>
@@ -59308,7 +59308,7 @@
       <c r="K828" t="inlineStr"/>
       <c r="L828" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M828" t="inlineStr"/>
@@ -59369,7 +59369,7 @@
       <c r="K829" t="inlineStr"/>
       <c r="L829" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M829" t="inlineStr"/>
@@ -59430,7 +59430,7 @@
       <c r="K830" t="inlineStr"/>
       <c r="L830" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M830" t="inlineStr"/>
@@ -59491,7 +59491,7 @@
       <c r="K831" t="inlineStr"/>
       <c r="L831" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M831" t="inlineStr"/>
@@ -59556,7 +59556,7 @@
       <c r="K832" t="inlineStr"/>
       <c r="L832" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M832" t="inlineStr">
@@ -59621,7 +59621,7 @@
       <c r="K833" t="inlineStr"/>
       <c r="L833" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M833" t="inlineStr"/>
@@ -59682,7 +59682,7 @@
       <c r="K834" t="inlineStr"/>
       <c r="L834" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M834" t="inlineStr"/>
@@ -59747,7 +59747,7 @@
       <c r="K835" t="inlineStr"/>
       <c r="L835" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M835" t="inlineStr">
@@ -59816,7 +59816,7 @@
       <c r="K836" t="inlineStr"/>
       <c r="L836" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M836" t="inlineStr">
@@ -59881,7 +59881,7 @@
       <c r="K837" t="inlineStr"/>
       <c r="L837" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M837" t="inlineStr"/>
@@ -59942,7 +59942,7 @@
       <c r="K838" t="inlineStr"/>
       <c r="L838" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M838" t="inlineStr"/>
@@ -60003,7 +60003,7 @@
       <c r="K839" t="inlineStr"/>
       <c r="L839" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M839" t="inlineStr"/>
@@ -60072,7 +60072,7 @@
       </c>
       <c r="L840" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M840" t="inlineStr">
@@ -60145,7 +60145,7 @@
       </c>
       <c r="L841" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M841" t="inlineStr">
@@ -60218,7 +60218,7 @@
       </c>
       <c r="L842" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M842" t="inlineStr">
@@ -60291,7 +60291,7 @@
       </c>
       <c r="L843" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M843" t="inlineStr">
@@ -60364,7 +60364,7 @@
       </c>
       <c r="L844" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M844" t="inlineStr">
@@ -60437,7 +60437,7 @@
       </c>
       <c r="L845" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M845" t="inlineStr">
@@ -60510,7 +60510,7 @@
       </c>
       <c r="L846" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M846" t="inlineStr">
@@ -60583,7 +60583,7 @@
       </c>
       <c r="L847" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M847" t="inlineStr">
@@ -60656,7 +60656,7 @@
       </c>
       <c r="L848" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M848" t="inlineStr">
@@ -60729,7 +60729,7 @@
       </c>
       <c r="L849" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M849" t="inlineStr">
@@ -60802,7 +60802,7 @@
       </c>
       <c r="L850" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M850" t="inlineStr">
@@ -60875,7 +60875,7 @@
       </c>
       <c r="L851" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M851" t="inlineStr">
@@ -60940,7 +60940,7 @@
       <c r="K852" t="inlineStr"/>
       <c r="L852" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M852" t="inlineStr"/>
@@ -61001,7 +61001,7 @@
       <c r="K853" t="inlineStr"/>
       <c r="L853" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M853" t="inlineStr"/>
@@ -61062,7 +61062,7 @@
       <c r="K854" t="inlineStr"/>
       <c r="L854" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M854" t="inlineStr"/>
@@ -61123,7 +61123,7 @@
       <c r="K855" t="inlineStr"/>
       <c r="L855" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M855" t="inlineStr"/>
@@ -61184,7 +61184,7 @@
       <c r="K856" t="inlineStr"/>
       <c r="L856" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M856" t="inlineStr"/>
@@ -61245,7 +61245,7 @@
       <c r="K857" t="inlineStr"/>
       <c r="L857" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M857" t="inlineStr"/>
@@ -61310,7 +61310,7 @@
       <c r="K858" t="inlineStr"/>
       <c r="L858" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M858" t="inlineStr">
@@ -61375,7 +61375,7 @@
       <c r="K859" t="inlineStr"/>
       <c r="L859" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M859" t="inlineStr"/>
@@ -61436,7 +61436,7 @@
       <c r="K860" t="inlineStr"/>
       <c r="L860" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M860" t="inlineStr"/>
@@ -61501,7 +61501,7 @@
       <c r="K861" t="inlineStr"/>
       <c r="L861" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M861" t="inlineStr">
@@ -61570,7 +61570,7 @@
       <c r="K862" t="inlineStr"/>
       <c r="L862" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M862" t="inlineStr">
@@ -61635,7 +61635,7 @@
       <c r="K863" t="inlineStr"/>
       <c r="L863" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M863" t="inlineStr"/>
@@ -61696,7 +61696,7 @@
       <c r="K864" t="inlineStr"/>
       <c r="L864" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M864" t="inlineStr"/>
@@ -61757,7 +61757,7 @@
       <c r="K865" t="inlineStr"/>
       <c r="L865" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M865" t="inlineStr"/>
@@ -61826,7 +61826,7 @@
       </c>
       <c r="L866" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M866" t="inlineStr">
@@ -61899,7 +61899,7 @@
       </c>
       <c r="L867" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M867" t="inlineStr">
@@ -61972,7 +61972,7 @@
       </c>
       <c r="L868" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M868" t="inlineStr">
@@ -62045,7 +62045,7 @@
       </c>
       <c r="L869" t="inlineStr">
         <is>
-          <t>ÉNFASIS 11°-02</t>
+          <t>ÉNFASIS 11°-2</t>
         </is>
       </c>
       <c r="M869" t="inlineStr">
@@ -62118,7 +62118,7 @@
       </c>
       <c r="L870" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M870" t="inlineStr">
@@ -62191,7 +62191,7 @@
       </c>
       <c r="L871" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M871" t="inlineStr">
@@ -62264,7 +62264,7 @@
       </c>
       <c r="L872" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M872" t="inlineStr">
@@ -62337,7 +62337,7 @@
       </c>
       <c r="L873" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 1-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M873" t="inlineStr">
@@ -62410,7 +62410,7 @@
       </c>
       <c r="L874" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M874" t="inlineStr">
@@ -62483,7 +62483,7 @@
       </c>
       <c r="L875" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M875" t="inlineStr">
@@ -62556,7 +62556,7 @@
       </c>
       <c r="L876" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M876" t="inlineStr">
@@ -62629,7 +62629,7 @@
       </c>
       <c r="L877" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-1</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M877" t="inlineStr">
@@ -62694,7 +62694,7 @@
       <c r="K878" t="inlineStr"/>
       <c r="L878" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M878" t="inlineStr"/>
@@ -62755,7 +62755,7 @@
       <c r="K879" t="inlineStr"/>
       <c r="L879" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M879" t="inlineStr"/>
@@ -62816,7 +62816,7 @@
       <c r="K880" t="inlineStr"/>
       <c r="L880" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M880" t="inlineStr"/>
@@ -62877,7 +62877,7 @@
       <c r="K881" t="inlineStr"/>
       <c r="L881" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M881" t="inlineStr"/>
@@ -62938,7 +62938,7 @@
       <c r="K882" t="inlineStr"/>
       <c r="L882" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M882" t="inlineStr"/>
@@ -62999,7 +62999,7 @@
       <c r="K883" t="inlineStr"/>
       <c r="L883" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M883" t="inlineStr"/>
@@ -63060,7 +63060,7 @@
       <c r="K884" t="inlineStr"/>
       <c r="L884" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M884" t="inlineStr"/>
@@ -63121,7 +63121,7 @@
       <c r="K885" t="inlineStr"/>
       <c r="L885" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M885" t="inlineStr"/>
@@ -63182,7 +63182,7 @@
       <c r="K886" t="inlineStr"/>
       <c r="L886" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M886" t="inlineStr"/>
@@ -63243,7 +63243,7 @@
       <c r="K887" t="inlineStr"/>
       <c r="L887" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M887" t="inlineStr"/>
@@ -63304,7 +63304,7 @@
       <c r="K888" t="inlineStr"/>
       <c r="L888" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M888" t="inlineStr"/>
@@ -63369,7 +63369,7 @@
       <c r="K889" t="inlineStr"/>
       <c r="L889" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M889" t="inlineStr">
@@ -63438,7 +63438,7 @@
       <c r="K890" t="inlineStr"/>
       <c r="L890" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M890" t="inlineStr">
@@ -63503,7 +63503,7 @@
       <c r="K891" t="inlineStr"/>
       <c r="L891" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M891" t="inlineStr"/>
@@ -63564,7 +63564,7 @@
       <c r="K892" t="inlineStr"/>
       <c r="L892" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M892" t="inlineStr"/>
@@ -63633,7 +63633,7 @@
       </c>
       <c r="L893" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M893" t="inlineStr">
@@ -63706,7 +63706,7 @@
       </c>
       <c r="L894" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M894" t="inlineStr">
@@ -63779,7 +63779,7 @@
       </c>
       <c r="L895" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M895" t="inlineStr">
@@ -63852,7 +63852,7 @@
       </c>
       <c r="L896" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M896" t="inlineStr">
@@ -63925,7 +63925,7 @@
       </c>
       <c r="L897" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M897" t="inlineStr">
@@ -63998,7 +63998,7 @@
       </c>
       <c r="L898" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M898" t="inlineStr">
@@ -64071,7 +64071,7 @@
       </c>
       <c r="L899" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M899" t="inlineStr">
@@ -64144,7 +64144,7 @@
       </c>
       <c r="L900" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M900" t="inlineStr">
@@ -64217,7 +64217,7 @@
       </c>
       <c r="L901" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M901" t="inlineStr">
@@ -64290,7 +64290,7 @@
       </c>
       <c r="L902" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M902" t="inlineStr">
@@ -64363,7 +64363,7 @@
       </c>
       <c r="L903" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M903" t="inlineStr">
@@ -64436,7 +64436,7 @@
       </c>
       <c r="L904" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M904" t="inlineStr">
@@ -64501,7 +64501,7 @@
       <c r="K905" t="inlineStr"/>
       <c r="L905" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M905" t="inlineStr"/>
@@ -64562,7 +64562,7 @@
       <c r="K906" t="inlineStr"/>
       <c r="L906" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M906" t="inlineStr"/>
@@ -64623,7 +64623,7 @@
       <c r="K907" t="inlineStr"/>
       <c r="L907" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M907" t="inlineStr"/>
@@ -64684,7 +64684,7 @@
       <c r="K908" t="inlineStr"/>
       <c r="L908" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M908" t="inlineStr"/>
@@ -64745,7 +64745,7 @@
       <c r="K909" t="inlineStr"/>
       <c r="L909" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M909" t="inlineStr"/>
@@ -64806,7 +64806,7 @@
       <c r="K910" t="inlineStr"/>
       <c r="L910" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M910" t="inlineStr"/>
@@ -64867,7 +64867,7 @@
       <c r="K911" t="inlineStr"/>
       <c r="L911" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M911" t="inlineStr"/>
@@ -64928,7 +64928,7 @@
       <c r="K912" t="inlineStr"/>
       <c r="L912" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M912" t="inlineStr"/>
@@ -64989,7 +64989,7 @@
       <c r="K913" t="inlineStr"/>
       <c r="L913" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M913" t="inlineStr"/>
@@ -65050,7 +65050,7 @@
       <c r="K914" t="inlineStr"/>
       <c r="L914" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M914" t="inlineStr"/>
@@ -65111,7 +65111,7 @@
       <c r="K915" t="inlineStr"/>
       <c r="L915" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M915" t="inlineStr"/>
@@ -65176,7 +65176,7 @@
       <c r="K916" t="inlineStr"/>
       <c r="L916" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M916" t="inlineStr">
@@ -65245,7 +65245,7 @@
       <c r="K917" t="inlineStr"/>
       <c r="L917" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M917" t="inlineStr">
@@ -65310,7 +65310,7 @@
       <c r="K918" t="inlineStr"/>
       <c r="L918" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M918" t="inlineStr"/>
@@ -65371,7 +65371,7 @@
       <c r="K919" t="inlineStr"/>
       <c r="L919" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M919" t="inlineStr"/>
@@ -65440,7 +65440,7 @@
       </c>
       <c r="L920" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M920" t="inlineStr">
@@ -65513,7 +65513,7 @@
       </c>
       <c r="L921" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M921" t="inlineStr">
@@ -65586,7 +65586,7 @@
       </c>
       <c r="L922" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M922" t="inlineStr">
@@ -65659,7 +65659,7 @@
       </c>
       <c r="L923" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-02</t>
+          <t>ÉNFASIS 8°-2</t>
         </is>
       </c>
       <c r="M923" t="inlineStr">
@@ -65732,7 +65732,7 @@
       </c>
       <c r="L924" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M924" t="inlineStr">
@@ -65805,7 +65805,7 @@
       </c>
       <c r="L925" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M925" t="inlineStr">
@@ -65878,7 +65878,7 @@
       </c>
       <c r="L926" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M926" t="inlineStr">
@@ -65951,7 +65951,7 @@
       </c>
       <c r="L927" t="inlineStr">
         <is>
-          <t>ÉNFASIS 9°-02</t>
+          <t>ÉNFASIS 9°-2</t>
         </is>
       </c>
       <c r="M927" t="inlineStr">
@@ -66024,7 +66024,7 @@
       </c>
       <c r="L928" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M928" t="inlineStr">
@@ -66097,7 +66097,7 @@
       </c>
       <c r="L929" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M929" t="inlineStr">
@@ -66170,7 +66170,7 @@
       </c>
       <c r="L930" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M930" t="inlineStr">
@@ -66243,7 +66243,7 @@
       </c>
       <c r="L931" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-02</t>
+          <t>ÉNFASIS 10°-2</t>
         </is>
       </c>
       <c r="M931" t="inlineStr">
@@ -66312,7 +66312,7 @@
       <c r="K932" t="inlineStr"/>
       <c r="L932" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M932" t="inlineStr">
@@ -66377,7 +66377,7 @@
       <c r="K933" t="inlineStr"/>
       <c r="L933" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M933" t="inlineStr"/>
@@ -66438,7 +66438,7 @@
       <c r="K934" t="inlineStr"/>
       <c r="L934" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M934" t="inlineStr"/>
@@ -66503,7 +66503,7 @@
       <c r="K935" t="inlineStr"/>
       <c r="L935" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M935" t="inlineStr">
@@ -66568,7 +66568,7 @@
       <c r="K936" t="inlineStr"/>
       <c r="L936" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M936" t="inlineStr"/>
@@ -66629,7 +66629,7 @@
       <c r="K937" t="inlineStr"/>
       <c r="L937" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M937" t="inlineStr"/>
@@ -66690,7 +66690,7 @@
       <c r="K938" t="inlineStr"/>
       <c r="L938" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M938" t="inlineStr"/>
@@ -66751,7 +66751,7 @@
       <c r="K939" t="inlineStr"/>
       <c r="L939" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M939" t="inlineStr"/>
@@ -66812,7 +66812,7 @@
       <c r="K940" t="inlineStr"/>
       <c r="L940" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M940" t="inlineStr"/>
@@ -66873,7 +66873,7 @@
       <c r="K941" t="inlineStr"/>
       <c r="L941" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M941" t="inlineStr"/>
@@ -66938,7 +66938,7 @@
       <c r="K942" t="inlineStr"/>
       <c r="L942" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M942" t="inlineStr">
@@ -67007,7 +67007,7 @@
       <c r="K943" t="inlineStr"/>
       <c r="L943" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M943" t="inlineStr">
@@ -67072,7 +67072,7 @@
       <c r="K944" t="inlineStr"/>
       <c r="L944" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M944" t="inlineStr"/>
@@ -67133,7 +67133,7 @@
       <c r="K945" t="inlineStr"/>
       <c r="L945" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M945" t="inlineStr"/>
@@ -67194,7 +67194,7 @@
       <c r="K946" t="inlineStr"/>
       <c r="L946" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M946" t="inlineStr"/>
@@ -67263,7 +67263,7 @@
       </c>
       <c r="L947" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M947" t="inlineStr">
@@ -67336,7 +67336,7 @@
       </c>
       <c r="L948" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M948" t="inlineStr">
@@ -67409,7 +67409,7 @@
       </c>
       <c r="L949" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M949" t="inlineStr">
@@ -67482,7 +67482,7 @@
       </c>
       <c r="L950" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M950" t="inlineStr">
@@ -67555,7 +67555,7 @@
       </c>
       <c r="L951" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M951" t="inlineStr">
@@ -67628,7 +67628,7 @@
       </c>
       <c r="L952" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M952" t="inlineStr">
@@ -67701,7 +67701,7 @@
       </c>
       <c r="L953" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M953" t="inlineStr">
@@ -67774,7 +67774,7 @@
       </c>
       <c r="L954" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M954" t="inlineStr">
@@ -67847,7 +67847,7 @@
       </c>
       <c r="L955" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M955" t="inlineStr">
@@ -67920,7 +67920,7 @@
       </c>
       <c r="L956" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M956" t="inlineStr">
@@ -67993,7 +67993,7 @@
       </c>
       <c r="L957" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M957" t="inlineStr">
@@ -68066,7 +68066,7 @@
       </c>
       <c r="L958" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M958" t="inlineStr">
@@ -68135,7 +68135,7 @@
       <c r="K959" t="inlineStr"/>
       <c r="L959" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="M959" t="inlineStr">
@@ -68200,7 +68200,7 @@
       <c r="K960" t="inlineStr"/>
       <c r="L960" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="M960" t="inlineStr"/>
@@ -68261,7 +68261,7 @@
       <c r="K961" t="inlineStr"/>
       <c r="L961" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M961" t="inlineStr"/>
@@ -68326,7 +68326,7 @@
       <c r="K962" t="inlineStr"/>
       <c r="L962" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M962" t="inlineStr">
@@ -68391,7 +68391,7 @@
       <c r="K963" t="inlineStr"/>
       <c r="L963" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M963" t="inlineStr"/>
@@ -68452,7 +68452,7 @@
       <c r="K964" t="inlineStr"/>
       <c r="L964" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M964" t="inlineStr"/>
@@ -68513,7 +68513,7 @@
       <c r="K965" t="inlineStr"/>
       <c r="L965" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M965" t="inlineStr"/>
@@ -68574,7 +68574,7 @@
       <c r="K966" t="inlineStr"/>
       <c r="L966" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M966" t="inlineStr"/>
@@ -68635,7 +68635,7 @@
       <c r="K967" t="inlineStr"/>
       <c r="L967" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M967" t="inlineStr"/>
@@ -68696,7 +68696,7 @@
       <c r="K968" t="inlineStr"/>
       <c r="L968" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M968" t="inlineStr"/>
@@ -68761,7 +68761,7 @@
       <c r="K969" t="inlineStr"/>
       <c r="L969" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M969" t="inlineStr">
@@ -68830,7 +68830,7 @@
       <c r="K970" t="inlineStr"/>
       <c r="L970" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M970" t="inlineStr">
@@ -68895,7 +68895,7 @@
       <c r="K971" t="inlineStr"/>
       <c r="L971" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M971" t="inlineStr"/>
@@ -68956,7 +68956,7 @@
       <c r="K972" t="inlineStr"/>
       <c r="L972" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M972" t="inlineStr"/>
@@ -69017,7 +69017,7 @@
       <c r="K973" t="inlineStr"/>
       <c r="L973" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M973" t="inlineStr"/>
@@ -69086,7 +69086,7 @@
       </c>
       <c r="L974" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M974" t="inlineStr">
@@ -69159,7 +69159,7 @@
       </c>
       <c r="L975" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M975" t="inlineStr">
@@ -69232,7 +69232,7 @@
       </c>
       <c r="L976" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M976" t="inlineStr">
@@ -69305,7 +69305,7 @@
       </c>
       <c r="L977" t="inlineStr">
         <is>
-          <t>ÉNFASIS 8°-01</t>
+          <t>ÉNFASIS 8°-1</t>
         </is>
       </c>
       <c r="M977" t="inlineStr">
@@ -69378,7 +69378,7 @@
       </c>
       <c r="L978" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M978" t="inlineStr">
@@ -69451,7 +69451,7 @@
       </c>
       <c r="L979" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M979" t="inlineStr">
@@ -69524,7 +69524,7 @@
       </c>
       <c r="L980" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M980" t="inlineStr">
@@ -69597,7 +69597,7 @@
       </c>
       <c r="L981" t="inlineStr">
         <is>
-          <t>ÉNFASIS 10°-01</t>
+          <t>ÉNFASIS 10°-1</t>
         </is>
       </c>
       <c r="M981" t="inlineStr">
@@ -69670,7 +69670,7 @@
       </c>
       <c r="L982" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M982" t="inlineStr">
@@ -69743,7 +69743,7 @@
       </c>
       <c r="L983" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M983" t="inlineStr">
@@ -69816,7 +69816,7 @@
       </c>
       <c r="L984" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M984" t="inlineStr">
@@ -69889,7 +69889,7 @@
       </c>
       <c r="L985" t="inlineStr">
         <is>
-          <t>ÉNFASIS CS 2-2</t>
+          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M985" t="inlineStr">
@@ -69954,7 +69954,7 @@
       <c r="K986" t="inlineStr"/>
       <c r="L986" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M986" t="inlineStr"/>
@@ -70019,7 +70019,7 @@
       <c r="K987" t="inlineStr"/>
       <c r="L987" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M987" t="inlineStr">
@@ -70084,7 +70084,7 @@
       <c r="K988" t="inlineStr"/>
       <c r="L988" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M988" t="inlineStr"/>
@@ -70149,7 +70149,7 @@
       <c r="K989" t="inlineStr"/>
       <c r="L989" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M989" t="inlineStr">
@@ -70214,7 +70214,7 @@
       <c r="K990" t="inlineStr"/>
       <c r="L990" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M990" t="inlineStr"/>
@@ -70275,7 +70275,7 @@
       <c r="K991" t="inlineStr"/>
       <c r="L991" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M991" t="inlineStr"/>
@@ -70340,7 +70340,7 @@
       <c r="K992" t="inlineStr"/>
       <c r="L992" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M992" t="inlineStr">
@@ -70405,7 +70405,7 @@
       <c r="K993" t="inlineStr"/>
       <c r="L993" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M993" t="inlineStr"/>
@@ -70466,7 +70466,7 @@
       <c r="K994" t="inlineStr"/>
       <c r="L994" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M994" t="inlineStr"/>
@@ -70527,7 +70527,7 @@
       <c r="K995" t="inlineStr"/>
       <c r="L995" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M995" t="inlineStr"/>
@@ -70592,7 +70592,7 @@
       <c r="K996" t="inlineStr"/>
       <c r="L996" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M996" t="inlineStr">
@@ -70657,7 +70657,7 @@
       <c r="K997" t="inlineStr"/>
       <c r="L997" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M997" t="inlineStr"/>
@@ -70718,7 +70718,7 @@
       <c r="K998" t="inlineStr"/>
       <c r="L998" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M998" t="inlineStr"/>
@@ -70779,7 +70779,7 @@
       <c r="K999" t="inlineStr"/>
       <c r="L999" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M999" t="inlineStr"/>
@@ -70840,7 +70840,7 @@
       <c r="K1000" t="inlineStr"/>
       <c r="L1000" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M1000" t="inlineStr"/>
@@ -70901,7 +70901,7 @@
       <c r="K1001" t="inlineStr"/>
       <c r="L1001" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M1001" t="inlineStr"/>
@@ -70970,7 +70970,7 @@
       </c>
       <c r="L1002" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-01</t>
+          <t>ÉNFASIS 6°-1</t>
         </is>
       </c>
       <c r="M1002" t="inlineStr">
@@ -71043,7 +71043,7 @@
       </c>
       <c r="L1003" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-01</t>
+          <t>ÉNFASIS 6°-1</t>
         </is>
       </c>
       <c r="M1003" t="inlineStr">
@@ -71116,7 +71116,7 @@
       </c>
       <c r="L1004" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-02</t>
+          <t>ÉNFASIS 6°-2</t>
         </is>
       </c>
       <c r="M1004" t="inlineStr">
@@ -71189,7 +71189,7 @@
       </c>
       <c r="L1005" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-02</t>
+          <t>ÉNFASIS 6°-2</t>
         </is>
       </c>
       <c r="M1005" t="inlineStr">
@@ -71254,7 +71254,7 @@
       <c r="K1006" t="inlineStr"/>
       <c r="L1006" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="M1006" t="inlineStr"/>
@@ -71319,7 +71319,7 @@
       <c r="K1007" t="inlineStr"/>
       <c r="L1007" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="M1007" t="inlineStr">
@@ -71384,7 +71384,7 @@
       <c r="K1008" t="inlineStr"/>
       <c r="L1008" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="M1008" t="inlineStr"/>
@@ -71449,7 +71449,7 @@
       <c r="K1009" t="inlineStr"/>
       <c r="L1009" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="M1009" t="inlineStr">
@@ -71514,7 +71514,7 @@
       <c r="K1010" t="inlineStr"/>
       <c r="L1010" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="M1010" t="inlineStr"/>
@@ -71575,7 +71575,7 @@
       <c r="K1011" t="inlineStr"/>
       <c r="L1011" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="M1011" t="inlineStr"/>
@@ -71640,7 +71640,7 @@
       <c r="K1012" t="inlineStr"/>
       <c r="L1012" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="M1012" t="inlineStr">
@@ -71705,7 +71705,7 @@
       <c r="K1013" t="inlineStr"/>
       <c r="L1013" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="M1013" t="inlineStr"/>
@@ -71766,7 +71766,7 @@
       <c r="K1014" t="inlineStr"/>
       <c r="L1014" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="M1014" t="inlineStr"/>
@@ -71827,7 +71827,7 @@
       <c r="K1015" t="inlineStr"/>
       <c r="L1015" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="M1015" t="inlineStr"/>
@@ -71892,7 +71892,7 @@
       <c r="K1016" t="inlineStr"/>
       <c r="L1016" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="M1016" t="inlineStr">
@@ -71957,7 +71957,7 @@
       <c r="K1017" t="inlineStr"/>
       <c r="L1017" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="M1017" t="inlineStr"/>
@@ -72018,7 +72018,7 @@
       <c r="K1018" t="inlineStr"/>
       <c r="L1018" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="M1018" t="inlineStr"/>
@@ -72079,7 +72079,7 @@
       <c r="K1019" t="inlineStr"/>
       <c r="L1019" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="M1019" t="inlineStr"/>
@@ -72140,7 +72140,7 @@
       <c r="K1020" t="inlineStr"/>
       <c r="L1020" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="M1020" t="inlineStr"/>
@@ -72201,7 +72201,7 @@
       <c r="K1021" t="inlineStr"/>
       <c r="L1021" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="M1021" t="inlineStr"/>
@@ -72270,7 +72270,7 @@
       </c>
       <c r="L1022" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-01</t>
+          <t>ÉNFASIS 6°-1</t>
         </is>
       </c>
       <c r="M1022" t="inlineStr">
@@ -72343,7 +72343,7 @@
       </c>
       <c r="L1023" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-01</t>
+          <t>ÉNFASIS 6°-1</t>
         </is>
       </c>
       <c r="M1023" t="inlineStr">
@@ -72416,7 +72416,7 @@
       </c>
       <c r="L1024" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-02</t>
+          <t>ÉNFASIS 6°-2</t>
         </is>
       </c>
       <c r="M1024" t="inlineStr">
@@ -72489,7 +72489,7 @@
       </c>
       <c r="L1025" t="inlineStr">
         <is>
-          <t>ÉNFASIS 6°-02</t>
+          <t>ÉNFASIS 6°-2</t>
         </is>
       </c>
       <c r="M1025" t="inlineStr">
@@ -72776,7 +72776,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -72805,7 +72805,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6°-01</t>
+          <t>6°-1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -72818,7 +72818,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6°-02</t>
+          <t>6°-2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -72826,12 +72826,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0701</t>
+          <t>CS101</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7°-01</t>
+          <t>Caminar en Secundaria 1-1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -72839,12 +72839,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0702</t>
+          <t>CS102</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7°-02</t>
+          <t>Caminar en Secundaria 1-2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -72852,12 +72852,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0703</t>
+          <t>0701</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7°-03</t>
+          <t>7°-1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -72865,12 +72865,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0704</t>
+          <t>0702</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7°-04</t>
+          <t>7°-2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -72878,12 +72878,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0801</t>
+          <t>0703</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8°-01</t>
+          <t>7°-3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -72891,12 +72891,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0802</t>
+          <t>0704</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8°-02</t>
+          <t>7°-4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -72904,12 +72904,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0901</t>
+          <t>0801</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>9°-01</t>
+          <t>8°-1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -72917,12 +72917,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0902</t>
+          <t>0802</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>9°-02</t>
+          <t>8°-2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -72930,12 +72930,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>0901</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10°-01</t>
+          <t>9°-1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -72943,12 +72943,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>0902</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10°-02</t>
+          <t>9°-2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -72956,12 +72956,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>CS201</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11°-01</t>
+          <t>Caminar en Secundaria 2-1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -72969,12 +72969,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>CS202</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11°-02</t>
+          <t>Caminar en Secundaria 2-2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -72982,12 +72982,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CS101</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CS 1-1</t>
+          <t>10°-1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -72995,12 +72995,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CS102</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CS 1-2</t>
+          <t>10°-2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -73008,12 +73008,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CS201</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CS 2-1</t>
+          <t>11°-1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -73021,12 +73021,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CS202</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CS 2-2</t>
+          <t>11°-2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>

--- a/ICET_Ubicacion_Docentes_Bachillerato.xlsx
+++ b/ICET_Ubicacion_Docentes_Bachillerato.xlsx
@@ -3427,7 +3427,7 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="36" customWidth="1" min="10" max="10"/>
     <col width="36" customWidth="1" min="11" max="11"/>
-    <col width="27" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
     <col width="36" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="24" customWidth="1" min="15" max="15"/>
@@ -4212,7 +4212,7 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -4273,7 +4273,7 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -4334,7 +4334,7 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -4395,7 +4395,7 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -5836,7 +5836,7 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
@@ -5897,7 +5897,7 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
@@ -5958,7 +5958,7 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
@@ -6019,7 +6019,7 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -7562,7 +7562,7 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7627,7 +7627,7 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
@@ -7688,7 +7688,7 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
@@ -7749,7 +7749,7 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M65" t="inlineStr"/>
@@ -9146,7 +9146,7 @@
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -9211,7 +9211,7 @@
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
@@ -9272,7 +9272,7 @@
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
@@ -9333,7 +9333,7 @@
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
@@ -10612,7 +10612,7 @@
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
@@ -10673,7 +10673,7 @@
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
@@ -10734,7 +10734,7 @@
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
@@ -10795,7 +10795,7 @@
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
@@ -12512,7 +12512,7 @@
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M136" t="inlineStr"/>
@@ -12573,7 +12573,7 @@
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M137" t="inlineStr"/>
@@ -12634,7 +12634,7 @@
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M138" t="inlineStr"/>
@@ -12695,7 +12695,7 @@
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M139" t="inlineStr"/>
@@ -14603,7 +14603,7 @@
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M167" t="inlineStr"/>
@@ -14664,7 +14664,7 @@
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M168" t="inlineStr"/>
@@ -14725,7 +14725,7 @@
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M169" t="inlineStr"/>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -15305,7 +15305,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -16195,7 +16195,7 @@
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M191" t="inlineStr"/>
@@ -16256,7 +16256,7 @@
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M192" t="inlineStr"/>
@@ -16317,7 +16317,7 @@
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M193" t="inlineStr"/>
@@ -16678,7 +16678,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -16751,7 +16751,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -16824,7 +16824,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -17515,7 +17515,7 @@
       <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -17580,7 +17580,7 @@
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M212" t="inlineStr"/>
@@ -18671,7 +18671,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
+          <t>ÉNFASIS CS 1-1</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -18744,7 +18744,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
+          <t>ÉNFASIS CS 1-1</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -18817,7 +18817,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
+          <t>ÉNFASIS CS 1-2</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -18890,7 +18890,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
+          <t>ÉNFASIS CS 1-2</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -19508,7 +19508,7 @@
       <c r="K240" t="inlineStr"/>
       <c r="L240" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -19573,7 +19573,7 @@
       <c r="K241" t="inlineStr"/>
       <c r="L241" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M241" t="inlineStr"/>
@@ -20664,7 +20664,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
+          <t>ÉNFASIS CS 1-1</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -20737,7 +20737,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
+          <t>ÉNFASIS CS 1-1</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -20810,7 +20810,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
+          <t>ÉNFASIS CS 1-2</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -20883,7 +20883,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
+          <t>ÉNFASIS CS 1-2</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
@@ -21712,7 +21712,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M272" t="inlineStr"/>
@@ -21777,7 +21777,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -21846,7 +21846,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -22503,7 +22503,7 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
@@ -22576,7 +22576,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -22649,7 +22649,7 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -22722,7 +22722,7 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -23551,7 +23551,7 @@
       <c r="K299" t="inlineStr"/>
       <c r="L299" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M299" t="inlineStr"/>
@@ -23616,7 +23616,7 @@
       <c r="K300" t="inlineStr"/>
       <c r="L300" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
@@ -23685,7 +23685,7 @@
       <c r="K301" t="inlineStr"/>
       <c r="L301" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
@@ -24342,7 +24342,7 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
@@ -24415,7 +24415,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -24488,7 +24488,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -24561,7 +24561,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -25378,7 +25378,7 @@
       <c r="K326" t="inlineStr"/>
       <c r="L326" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
@@ -25443,7 +25443,7 @@
       <c r="K327" t="inlineStr"/>
       <c r="L327" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M327" t="inlineStr"/>
@@ -25504,7 +25504,7 @@
       <c r="K328" t="inlineStr"/>
       <c r="L328" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M328" t="inlineStr"/>
@@ -26011,7 +26011,7 @@
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
@@ -26084,7 +26084,7 @@
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
@@ -26157,7 +26157,7 @@
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
@@ -26230,7 +26230,7 @@
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
@@ -27047,7 +27047,7 @@
       <c r="K351" t="inlineStr"/>
       <c r="L351" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
@@ -27112,7 +27112,7 @@
       <c r="K352" t="inlineStr"/>
       <c r="L352" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M352" t="inlineStr"/>
@@ -27173,7 +27173,7 @@
       <c r="K353" t="inlineStr"/>
       <c r="L353" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M353" t="inlineStr"/>
@@ -27680,7 +27680,7 @@
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M360" t="inlineStr">
@@ -27753,7 +27753,7 @@
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
@@ -27826,7 +27826,7 @@
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
@@ -27899,7 +27899,7 @@
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
@@ -28606,7 +28606,7 @@
       <c r="K374" t="inlineStr"/>
       <c r="L374" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M374" t="inlineStr"/>
@@ -28667,7 +28667,7 @@
       <c r="K375" t="inlineStr"/>
       <c r="L375" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M375" t="inlineStr"/>
@@ -28728,7 +28728,7 @@
       <c r="K376" t="inlineStr"/>
       <c r="L376" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M376" t="inlineStr"/>
@@ -28793,7 +28793,7 @@
       <c r="K377" t="inlineStr"/>
       <c r="L377" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
@@ -30376,7 +30376,7 @@
       <c r="K400" t="inlineStr"/>
       <c r="L400" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M400" t="inlineStr"/>
@@ -30437,7 +30437,7 @@
       <c r="K401" t="inlineStr"/>
       <c r="L401" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M401" t="inlineStr"/>
@@ -30498,7 +30498,7 @@
       <c r="K402" t="inlineStr"/>
       <c r="L402" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M402" t="inlineStr"/>
@@ -30563,7 +30563,7 @@
       <c r="K403" t="inlineStr"/>
       <c r="L403" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M403" t="inlineStr">
@@ -32183,7 +32183,7 @@
       <c r="K427" t="inlineStr"/>
       <c r="L427" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M427" t="inlineStr"/>
@@ -32248,7 +32248,7 @@
       <c r="K428" t="inlineStr"/>
       <c r="L428" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M428" t="inlineStr">
@@ -32759,7 +32759,7 @@
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
+          <t>ÉNFASIS CS 1-1</t>
         </is>
       </c>
       <c r="M435" t="inlineStr">
@@ -32832,7 +32832,7 @@
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
+          <t>ÉNFASIS CS 1-1</t>
         </is>
       </c>
       <c r="M436" t="inlineStr">
@@ -32905,7 +32905,7 @@
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
+          <t>ÉNFASIS CS 1-2</t>
         </is>
       </c>
       <c r="M437" t="inlineStr">
@@ -32978,7 +32978,7 @@
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
+          <t>ÉNFASIS CS 1-2</t>
         </is>
       </c>
       <c r="M438" t="inlineStr">
@@ -33722,7 +33722,7 @@
       <c r="K450" t="inlineStr"/>
       <c r="L450" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M450" t="inlineStr"/>
@@ -33787,7 +33787,7 @@
       <c r="K451" t="inlineStr"/>
       <c r="L451" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M451" t="inlineStr">
@@ -34298,7 +34298,7 @@
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
+          <t>ÉNFASIS CS 1-1</t>
         </is>
       </c>
       <c r="M458" t="inlineStr">
@@ -34371,7 +34371,7 @@
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
+          <t>ÉNFASIS CS 1-1</t>
         </is>
       </c>
       <c r="M459" t="inlineStr">
@@ -34444,7 +34444,7 @@
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
+          <t>ÉNFASIS CS 1-2</t>
         </is>
       </c>
       <c r="M460" t="inlineStr">
@@ -34517,7 +34517,7 @@
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
+          <t>ÉNFASIS CS 1-2</t>
         </is>
       </c>
       <c r="M461" t="inlineStr">
@@ -35322,7 +35322,7 @@
       <c r="K474" t="inlineStr"/>
       <c r="L474" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M474" t="inlineStr"/>
@@ -35387,7 +35387,7 @@
       <c r="K475" t="inlineStr"/>
       <c r="L475" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M475" t="inlineStr">
@@ -35456,7 +35456,7 @@
       <c r="K476" t="inlineStr"/>
       <c r="L476" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M476" t="inlineStr">
@@ -36113,7 +36113,7 @@
       </c>
       <c r="L485" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M485" t="inlineStr">
@@ -36186,7 +36186,7 @@
       </c>
       <c r="L486" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M486" t="inlineStr">
@@ -36259,7 +36259,7 @@
       </c>
       <c r="L487" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M487" t="inlineStr">
@@ -36332,7 +36332,7 @@
       </c>
       <c r="L488" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M488" t="inlineStr">
@@ -37137,7 +37137,7 @@
       <c r="K501" t="inlineStr"/>
       <c r="L501" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M501" t="inlineStr"/>
@@ -37202,7 +37202,7 @@
       <c r="K502" t="inlineStr"/>
       <c r="L502" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M502" t="inlineStr">
@@ -37271,7 +37271,7 @@
       <c r="K503" t="inlineStr"/>
       <c r="L503" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M503" t="inlineStr">
@@ -37928,7 +37928,7 @@
       </c>
       <c r="L512" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M512" t="inlineStr">
@@ -38001,7 +38001,7 @@
       </c>
       <c r="L513" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M513" t="inlineStr">
@@ -38074,7 +38074,7 @@
       </c>
       <c r="L514" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M514" t="inlineStr">
@@ -38147,7 +38147,7 @@
       </c>
       <c r="L515" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M515" t="inlineStr">
@@ -38907,7 +38907,7 @@
       <c r="K527" t="inlineStr"/>
       <c r="L527" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M527" t="inlineStr"/>
@@ -38968,7 +38968,7 @@
       <c r="K528" t="inlineStr"/>
       <c r="L528" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M528" t="inlineStr"/>
@@ -39029,7 +39029,7 @@
       <c r="K529" t="inlineStr"/>
       <c r="L529" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M529" t="inlineStr"/>
@@ -39090,7 +39090,7 @@
       <c r="K530" t="inlineStr"/>
       <c r="L530" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M530" t="inlineStr"/>
@@ -40576,7 +40576,7 @@
       <c r="K552" t="inlineStr"/>
       <c r="L552" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M552" t="inlineStr"/>
@@ -40637,7 +40637,7 @@
       <c r="K553" t="inlineStr"/>
       <c r="L553" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M553" t="inlineStr"/>
@@ -40698,7 +40698,7 @@
       <c r="K554" t="inlineStr"/>
       <c r="L554" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M554" t="inlineStr"/>
@@ -40759,7 +40759,7 @@
       <c r="K555" t="inlineStr"/>
       <c r="L555" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M555" t="inlineStr"/>
@@ -42139,7 +42139,7 @@
       <c r="K575" t="inlineStr"/>
       <c r="L575" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M575" t="inlineStr"/>
@@ -42204,7 +42204,7 @@
       <c r="K576" t="inlineStr"/>
       <c r="L576" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M576" t="inlineStr">
@@ -42269,7 +42269,7 @@
       <c r="K577" t="inlineStr"/>
       <c r="L577" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M577" t="inlineStr"/>
@@ -42330,7 +42330,7 @@
       <c r="K578" t="inlineStr"/>
       <c r="L578" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M578" t="inlineStr"/>
@@ -44148,7 +44148,7 @@
       <c r="K604" t="inlineStr"/>
       <c r="L604" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M604" t="inlineStr"/>
@@ -44213,7 +44213,7 @@
       <c r="K605" t="inlineStr"/>
       <c r="L605" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M605" t="inlineStr">
@@ -44278,7 +44278,7 @@
       <c r="K606" t="inlineStr"/>
       <c r="L606" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M606" t="inlineStr"/>
@@ -44339,7 +44339,7 @@
       <c r="K607" t="inlineStr"/>
       <c r="L607" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M607" t="inlineStr"/>
@@ -46186,7 +46186,7 @@
       <c r="K634" t="inlineStr"/>
       <c r="L634" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M634" t="inlineStr"/>
@@ -46251,7 +46251,7 @@
       <c r="K635" t="inlineStr"/>
       <c r="L635" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M635" t="inlineStr">
@@ -47054,7 +47054,7 @@
       </c>
       <c r="L646" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
+          <t>ÉNFASIS CS 1-1</t>
         </is>
       </c>
       <c r="M646" t="inlineStr">
@@ -47127,7 +47127,7 @@
       </c>
       <c r="L647" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
+          <t>ÉNFASIS CS 1-1</t>
         </is>
       </c>
       <c r="M647" t="inlineStr">
@@ -47200,7 +47200,7 @@
       </c>
       <c r="L648" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
+          <t>ÉNFASIS CS 1-2</t>
         </is>
       </c>
       <c r="M648" t="inlineStr">
@@ -47273,7 +47273,7 @@
       </c>
       <c r="L649" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
+          <t>ÉNFASIS CS 1-2</t>
         </is>
       </c>
       <c r="M649" t="inlineStr">
@@ -47956,7 +47956,7 @@
       <c r="K660" t="inlineStr"/>
       <c r="L660" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M660" t="inlineStr"/>
@@ -48021,7 +48021,7 @@
       <c r="K661" t="inlineStr"/>
       <c r="L661" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M661" t="inlineStr">
@@ -48824,7 +48824,7 @@
       </c>
       <c r="L672" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
+          <t>ÉNFASIS CS 1-1</t>
         </is>
       </c>
       <c r="M672" t="inlineStr">
@@ -48897,7 +48897,7 @@
       </c>
       <c r="L673" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
+          <t>ÉNFASIS CS 1-1</t>
         </is>
       </c>
       <c r="M673" t="inlineStr">
@@ -48970,7 +48970,7 @@
       </c>
       <c r="L674" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
+          <t>ÉNFASIS CS 1-2</t>
         </is>
       </c>
       <c r="M674" t="inlineStr">
@@ -49043,7 +49043,7 @@
       </c>
       <c r="L675" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
+          <t>ÉNFASIS CS 1-2</t>
         </is>
       </c>
       <c r="M675" t="inlineStr">
@@ -49941,7 +49941,7 @@
       <c r="K689" t="inlineStr"/>
       <c r="L689" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M689" t="inlineStr"/>
@@ -50002,7 +50002,7 @@
       <c r="K690" t="inlineStr"/>
       <c r="L690" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M690" t="inlineStr"/>
@@ -50067,7 +50067,7 @@
       <c r="K691" t="inlineStr"/>
       <c r="L691" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M691" t="inlineStr">
@@ -50132,7 +50132,7 @@
       <c r="K692" t="inlineStr"/>
       <c r="L692" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M692" t="inlineStr"/>
@@ -51318,7 +51318,7 @@
       <c r="K710" t="inlineStr"/>
       <c r="L710" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M710" t="inlineStr"/>
@@ -51379,7 +51379,7 @@
       <c r="K711" t="inlineStr"/>
       <c r="L711" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M711" t="inlineStr"/>
@@ -51444,7 +51444,7 @@
       <c r="K712" t="inlineStr"/>
       <c r="L712" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M712" t="inlineStr">
@@ -51509,7 +51509,7 @@
       <c r="K713" t="inlineStr"/>
       <c r="L713" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M713" t="inlineStr"/>
@@ -52549,7 +52549,7 @@
       <c r="K729" t="inlineStr"/>
       <c r="L729" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M729" t="inlineStr"/>
@@ -52610,7 +52610,7 @@
       <c r="K730" t="inlineStr"/>
       <c r="L730" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M730" t="inlineStr"/>
@@ -52675,7 +52675,7 @@
       <c r="K731" t="inlineStr"/>
       <c r="L731" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M731" t="inlineStr">
@@ -53478,7 +53478,7 @@
       </c>
       <c r="L742" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M742" t="inlineStr">
@@ -53551,7 +53551,7 @@
       </c>
       <c r="L743" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M743" t="inlineStr">
@@ -53624,7 +53624,7 @@
       </c>
       <c r="L744" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M744" t="inlineStr">
@@ -53697,7 +53697,7 @@
       </c>
       <c r="L745" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M745" t="inlineStr">
@@ -54449,7 +54449,7 @@
       <c r="K757" t="inlineStr"/>
       <c r="L757" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M757" t="inlineStr"/>
@@ -54510,7 +54510,7 @@
       <c r="K758" t="inlineStr"/>
       <c r="L758" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M758" t="inlineStr"/>
@@ -54575,7 +54575,7 @@
       <c r="K759" t="inlineStr"/>
       <c r="L759" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M759" t="inlineStr">
@@ -55378,7 +55378,7 @@
       </c>
       <c r="L770" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M770" t="inlineStr">
@@ -55451,7 +55451,7 @@
       </c>
       <c r="L771" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M771" t="inlineStr">
@@ -55524,7 +55524,7 @@
       </c>
       <c r="L772" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M772" t="inlineStr">
@@ -55597,7 +55597,7 @@
       </c>
       <c r="L773" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M773" t="inlineStr">
@@ -56361,7 +56361,7 @@
       <c r="K785" t="inlineStr"/>
       <c r="L785" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M785" t="inlineStr">
@@ -56426,7 +56426,7 @@
       <c r="K786" t="inlineStr"/>
       <c r="L786" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M786" t="inlineStr"/>
@@ -56487,7 +56487,7 @@
       <c r="K787" t="inlineStr"/>
       <c r="L787" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M787" t="inlineStr"/>
@@ -57140,7 +57140,7 @@
       </c>
       <c r="L796" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M796" t="inlineStr">
@@ -57213,7 +57213,7 @@
       </c>
       <c r="L797" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M797" t="inlineStr">
@@ -57286,7 +57286,7 @@
       </c>
       <c r="L798" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M798" t="inlineStr">
@@ -57359,7 +57359,7 @@
       </c>
       <c r="L799" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M799" t="inlineStr">
@@ -58123,7 +58123,7 @@
       <c r="K811" t="inlineStr"/>
       <c r="L811" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M811" t="inlineStr">
@@ -58188,7 +58188,7 @@
       <c r="K812" t="inlineStr"/>
       <c r="L812" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M812" t="inlineStr"/>
@@ -58249,7 +58249,7 @@
       <c r="K813" t="inlineStr"/>
       <c r="L813" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M813" t="inlineStr"/>
@@ -58902,7 +58902,7 @@
       </c>
       <c r="L822" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M822" t="inlineStr">
@@ -58975,7 +58975,7 @@
       </c>
       <c r="L823" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M823" t="inlineStr">
@@ -59048,7 +59048,7 @@
       </c>
       <c r="L824" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M824" t="inlineStr">
@@ -59121,7 +59121,7 @@
       </c>
       <c r="L825" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M825" t="inlineStr">
@@ -60003,7 +60003,7 @@
       <c r="K839" t="inlineStr"/>
       <c r="L839" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M839" t="inlineStr"/>
@@ -60364,7 +60364,7 @@
       </c>
       <c r="L844" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
+          <t>ÉNFASIS CS 1-1</t>
         </is>
       </c>
       <c r="M844" t="inlineStr">
@@ -60437,7 +60437,7 @@
       </c>
       <c r="L845" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
+          <t>ÉNFASIS CS 1-1</t>
         </is>
       </c>
       <c r="M845" t="inlineStr">
@@ -60510,7 +60510,7 @@
       </c>
       <c r="L846" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
+          <t>ÉNFASIS CS 1-2</t>
         </is>
       </c>
       <c r="M846" t="inlineStr">
@@ -60583,7 +60583,7 @@
       </c>
       <c r="L847" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
+          <t>ÉNFASIS CS 1-2</t>
         </is>
       </c>
       <c r="M847" t="inlineStr">
@@ -60656,7 +60656,7 @@
       </c>
       <c r="L848" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M848" t="inlineStr">
@@ -60729,7 +60729,7 @@
       </c>
       <c r="L849" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M849" t="inlineStr">
@@ -60802,7 +60802,7 @@
       </c>
       <c r="L850" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M850" t="inlineStr">
@@ -60875,7 +60875,7 @@
       </c>
       <c r="L851" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M851" t="inlineStr">
@@ -61757,7 +61757,7 @@
       <c r="K865" t="inlineStr"/>
       <c r="L865" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M865" t="inlineStr"/>
@@ -62118,7 +62118,7 @@
       </c>
       <c r="L870" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
+          <t>ÉNFASIS CS 1-1</t>
         </is>
       </c>
       <c r="M870" t="inlineStr">
@@ -62191,7 +62191,7 @@
       </c>
       <c r="L871" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-1</t>
+          <t>ÉNFASIS CS 1-1</t>
         </is>
       </c>
       <c r="M871" t="inlineStr">
@@ -62264,7 +62264,7 @@
       </c>
       <c r="L872" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
+          <t>ÉNFASIS CS 1-2</t>
         </is>
       </c>
       <c r="M872" t="inlineStr">
@@ -62337,7 +62337,7 @@
       </c>
       <c r="L873" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 1-2</t>
+          <t>ÉNFASIS CS 1-2</t>
         </is>
       </c>
       <c r="M873" t="inlineStr">
@@ -62410,7 +62410,7 @@
       </c>
       <c r="L874" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M874" t="inlineStr">
@@ -62483,7 +62483,7 @@
       </c>
       <c r="L875" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M875" t="inlineStr">
@@ -62556,7 +62556,7 @@
       </c>
       <c r="L876" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M876" t="inlineStr">
@@ -62629,7 +62629,7 @@
       </c>
       <c r="L877" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-1</t>
+          <t>ÉNFASIS CS 2-1</t>
         </is>
       </c>
       <c r="M877" t="inlineStr">
@@ -63369,7 +63369,7 @@
       <c r="K889" t="inlineStr"/>
       <c r="L889" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M889" t="inlineStr">
@@ -63438,7 +63438,7 @@
       <c r="K890" t="inlineStr"/>
       <c r="L890" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M890" t="inlineStr">
@@ -63503,7 +63503,7 @@
       <c r="K891" t="inlineStr"/>
       <c r="L891" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M891" t="inlineStr"/>
@@ -63564,7 +63564,7 @@
       <c r="K892" t="inlineStr"/>
       <c r="L892" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M892" t="inlineStr"/>
@@ -65176,7 +65176,7 @@
       <c r="K916" t="inlineStr"/>
       <c r="L916" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M916" t="inlineStr">
@@ -65245,7 +65245,7 @@
       <c r="K917" t="inlineStr"/>
       <c r="L917" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M917" t="inlineStr">
@@ -65310,7 +65310,7 @@
       <c r="K918" t="inlineStr"/>
       <c r="L918" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M918" t="inlineStr"/>
@@ -65371,7 +65371,7 @@
       <c r="K919" t="inlineStr"/>
       <c r="L919" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M919" t="inlineStr"/>
@@ -67072,7 +67072,7 @@
       <c r="K944" t="inlineStr"/>
       <c r="L944" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M944" t="inlineStr"/>
@@ -67133,7 +67133,7 @@
       <c r="K945" t="inlineStr"/>
       <c r="L945" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M945" t="inlineStr"/>
@@ -67194,7 +67194,7 @@
       <c r="K946" t="inlineStr"/>
       <c r="L946" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M946" t="inlineStr"/>
@@ -67847,7 +67847,7 @@
       </c>
       <c r="L955" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M955" t="inlineStr">
@@ -67920,7 +67920,7 @@
       </c>
       <c r="L956" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M956" t="inlineStr">
@@ -67993,7 +67993,7 @@
       </c>
       <c r="L957" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M957" t="inlineStr">
@@ -68066,7 +68066,7 @@
       </c>
       <c r="L958" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M958" t="inlineStr">
@@ -68895,7 +68895,7 @@
       <c r="K971" t="inlineStr"/>
       <c r="L971" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M971" t="inlineStr"/>
@@ -68956,7 +68956,7 @@
       <c r="K972" t="inlineStr"/>
       <c r="L972" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M972" t="inlineStr"/>
@@ -69017,7 +69017,7 @@
       <c r="K973" t="inlineStr"/>
       <c r="L973" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M973" t="inlineStr"/>
@@ -69670,7 +69670,7 @@
       </c>
       <c r="L982" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M982" t="inlineStr">
@@ -69743,7 +69743,7 @@
       </c>
       <c r="L983" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M983" t="inlineStr">
@@ -69816,7 +69816,7 @@
       </c>
       <c r="L984" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M984" t="inlineStr">
@@ -69889,7 +69889,7 @@
       </c>
       <c r="L985" t="inlineStr">
         <is>
-          <t>ÉNFASIS Caminar en Secundaria 2-2</t>
+          <t>ÉNFASIS CS 2-2</t>
         </is>
       </c>
       <c r="M985" t="inlineStr">
@@ -70718,7 +70718,7 @@
       <c r="K998" t="inlineStr"/>
       <c r="L998" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M998" t="inlineStr"/>
@@ -70779,7 +70779,7 @@
       <c r="K999" t="inlineStr"/>
       <c r="L999" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M999" t="inlineStr"/>
@@ -70840,7 +70840,7 @@
       <c r="K1000" t="inlineStr"/>
       <c r="L1000" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M1000" t="inlineStr"/>
@@ -70901,7 +70901,7 @@
       <c r="K1001" t="inlineStr"/>
       <c r="L1001" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M1001" t="inlineStr"/>
@@ -72018,7 +72018,7 @@
       <c r="K1018" t="inlineStr"/>
       <c r="L1018" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="M1018" t="inlineStr"/>
@@ -72079,7 +72079,7 @@
       <c r="K1019" t="inlineStr"/>
       <c r="L1019" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="M1019" t="inlineStr"/>
@@ -72140,7 +72140,7 @@
       <c r="K1020" t="inlineStr"/>
       <c r="L1020" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="M1020" t="inlineStr"/>
@@ -72201,7 +72201,7 @@
       <c r="K1021" t="inlineStr"/>
       <c r="L1021" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="M1021" t="inlineStr"/>
@@ -72776,7 +72776,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -72831,7 +72831,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-1</t>
+          <t>CS 1-1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -72844,7 +72844,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 1-2</t>
+          <t>CS 1-2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -72961,7 +72961,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-1</t>
+          <t>CS 2-1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -72974,7 +72974,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Caminar en Secundaria 2-2</t>
+          <t>CS 2-2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>

--- a/ICET_Ubicacion_Docentes_Bachillerato.xlsx
+++ b/ICET_Ubicacion_Docentes_Bachillerato.xlsx
@@ -4637,11 +4637,11 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Armero Dájome Jesús</t>
+          <t>Arizala Castro Roberto Carlos</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -6261,11 +6261,11 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Armero Dájome Jesús</t>
+          <t>Arizala Castro Roberto Carlos</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6955,11 +6955,11 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Armero Dájome Jesús</t>
+          <t>Arizala Castro Roberto Carlos</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7589,11 +7589,11 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Arizala Castro Roberto Carlos</t>
+          <t>Armero Dájome Jesús</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8539,11 +8539,11 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Armero Dájome Jesús</t>
+          <t>Arizala Castro Roberto Carlos</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -9173,11 +9173,11 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Arizala Castro Roberto Carlos</t>
+          <t>Armero Dájome Jesús</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -9940,11 +9940,11 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Arizala Castro Roberto Carlos</t>
+          <t>Armero Dájome Jesús</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -10192,11 +10192,11 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Armero Dájome Jesús</t>
+          <t>Arizala Castro Roberto Carlos</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -11840,11 +11840,11 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Arizala Castro Roberto Carlos</t>
+          <t>Armero Dájome Jesús</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -12092,11 +12092,11 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Armero Dájome Jesús</t>
+          <t>Arizala Castro Roberto Carlos</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -14565,11 +14565,11 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Arizala Castro Roberto Carlos</t>
+          <t>Armero Dájome Jesús</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -16157,11 +16157,11 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Arizala Castro Roberto Carlos</t>
+          <t>Armero Dájome Jesús</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -17046,11 +17046,11 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Armero Dájome Jesús</t>
+          <t>Arizala Castro Roberto Carlos</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -19039,11 +19039,11 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Armero Dájome Jesús</t>
+          <t>Arizala Castro Roberto Carlos</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -25405,11 +25405,11 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Arizala Castro Roberto Carlos</t>
+          <t>Armero Dájome Jesús</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -27074,11 +27074,11 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Arizala Castro Roberto Carlos</t>
+          <t>Armero Dájome Jesús</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -29039,11 +29039,11 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Armero Dájome Jesús</t>
+          <t>Arizala Castro Roberto Carlos</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -30809,11 +30809,11 @@
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Armero Dájome Jesús</t>
+          <t>Arizala Castro Roberto Carlos</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -31527,11 +31527,11 @@
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Arizala Castro Roberto Carlos</t>
+          <t>Armero Dájome Jesús</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -33066,11 +33066,11 @@
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Arizala Castro Roberto Carlos</t>
+          <t>Armero Dájome Jesús</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -34849,11 +34849,11 @@
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Armero Dájome Jesús</t>
+          <t>Arizala Castro Roberto Carlos</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -36664,11 +36664,11 @@
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Armero Dájome Jesús</t>
+          <t>Arizala Castro Roberto Carlos</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -38442,11 +38442,11 @@
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Armero Dájome Jesús</t>
+          <t>Arizala Castro Roberto Carlos</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -38869,11 +38869,11 @@
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Arizala Castro Roberto Carlos</t>
+          <t>Armero Dájome Jesús</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -40111,11 +40111,11 @@
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Armero Dájome Jesús</t>
+          <t>Arizala Castro Roberto Carlos</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -40538,11 +40538,11 @@
     </row>
     <row r="552">
       <c r="A552" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Arizala Castro Roberto Carlos</t>
+          <t>Armero Dájome Jesús</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -42572,11 +42572,11 @@
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Armero Dájome Jesús</t>
+          <t>Arizala Castro Roberto Carlos</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -44581,11 +44581,11 @@
     </row>
     <row r="611">
       <c r="A611" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Armero Dájome Jesús</t>
+          <t>Arizala Castro Roberto Carlos</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -46497,11 +46497,11 @@
     </row>
     <row r="639">
       <c r="A639" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Armero Dájome Jesús</t>
+          <t>Arizala Castro Roberto Carlos</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -48267,11 +48267,11 @@
     </row>
     <row r="665">
       <c r="A665" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Armero Dájome Jesús</t>
+          <t>Arizala Castro Roberto Carlos</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -49070,11 +49070,11 @@
     </row>
     <row r="676">
       <c r="A676" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>Arizala Castro Roberto Carlos</t>
+          <t>Armero Dájome Jesús</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -49200,11 +49200,11 @@
     </row>
     <row r="678">
       <c r="A678" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Armero Dájome Jesús</t>
+          <t>Arizala Castro Roberto Carlos</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -50447,11 +50447,11 @@
     </row>
     <row r="697">
       <c r="A697" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Arizala Castro Roberto Carlos</t>
+          <t>Armero Dájome Jesús</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -50577,11 +50577,11 @@
     </row>
     <row r="699">
       <c r="A699" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Armero Dájome Jesús</t>
+          <t>Arizala Castro Roberto Carlos</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -52015,11 +52015,11 @@
     </row>
     <row r="721">
       <c r="A721" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Armero Dájome Jesús</t>
+          <t>Arizala Castro Roberto Carlos</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -53915,11 +53915,11 @@
     </row>
     <row r="749">
       <c r="A749" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>Armero Dájome Jesús</t>
+          <t>Arizala Castro Roberto Carlos</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -56729,11 +56729,11 @@
     </row>
     <row r="791">
       <c r="A791" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>Armero Dájome Jesús</t>
+          <t>Arizala Castro Roberto Carlos</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -58491,11 +58491,11 @@
     </row>
     <row r="817">
       <c r="A817" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>Armero Dájome Jesús</t>
+          <t>Arizala Castro Roberto Carlos</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -59270,11 +59270,11 @@
     </row>
     <row r="828">
       <c r="A828" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>Armero Dájome Jesús</t>
+          <t>Arizala Castro Roberto Carlos</t>
         </is>
       </c>
       <c r="C828" t="inlineStr">
@@ -61024,11 +61024,11 @@
     </row>
     <row r="854">
       <c r="A854" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>Armero Dájome Jesús</t>
+          <t>Arizala Castro Roberto Carlos</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
@@ -66339,11 +66339,11 @@
     </row>
     <row r="933">
       <c r="A933" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>Arizala Castro Roberto Carlos</t>
+          <t>Armero Dájome Jesús</t>
         </is>
       </c>
       <c r="C933" t="inlineStr">
@@ -68162,11 +68162,11 @@
     </row>
     <row r="960">
       <c r="A960" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t>Arizala Castro Roberto Carlos</t>
+          <t>Armero Dájome Jesús</t>
         </is>
       </c>
       <c r="C960" t="inlineStr">
@@ -71143,11 +71143,11 @@
     </row>
     <row r="1005">
       <c r="A1005" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>Armero Dájome Jesús</t>
+          <t>Arizala Castro Roberto Carlos</t>
         </is>
       </c>
       <c r="C1005" t="inlineStr">
@@ -72443,11 +72443,11 @@
     </row>
     <row r="1025">
       <c r="A1025" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t>Armero Dájome Jesús</t>
+          <t>Arizala Castro Roberto Carlos</t>
         </is>
       </c>
       <c r="C1025" t="inlineStr">

--- a/ICET_Ubicacion_Docentes_Bachillerato.xlsx
+++ b/ICET_Ubicacion_Docentes_Bachillerato.xlsx
@@ -28629,11 +28629,11 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Arizala Castro Roberto Carlos</t>
+          <t>Armero Dájome Jesús</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -30399,11 +30399,11 @@
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Arizala Castro Roberto Carlos</t>
+          <t>Armero Dájome Jesús</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -35284,11 +35284,11 @@
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Arizala Castro Roberto Carlos</t>
+          <t>Armero Dájome Jesús</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -37099,11 +37099,11 @@
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Arizala Castro Roberto Carlos</t>
+          <t>Armero Dájome Jesús</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -52572,11 +52572,11 @@
     </row>
     <row r="730">
       <c r="A730" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>Arizala Castro Roberto Carlos</t>
+          <t>Armero Dájome Jesús</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -54472,11 +54472,11 @@
     </row>
     <row r="758">
       <c r="A758" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>Arizala Castro Roberto Carlos</t>
+          <t>Armero Dájome Jesús</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -70680,11 +70680,11 @@
     </row>
     <row r="998">
       <c r="A998" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t>Arizala Castro Roberto Carlos</t>
+          <t>Armero Dájome Jesús</t>
         </is>
       </c>
       <c r="C998" t="inlineStr">
@@ -71980,11 +71980,11 @@
     </row>
     <row r="1018">
       <c r="A1018" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="B1018" t="inlineStr">
         <is>
-          <t>Arizala Castro Roberto Carlos</t>
+          <t>Armero Dájome Jesús</t>
         </is>
       </c>
       <c r="C1018" t="inlineStr">
